--- a/03_IE_tasks/data/related/outcomes_endpoints/harmonized_synonyms_GPT.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/harmonized_synonyms_GPT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC517C0-4C6A-A741-9C87-F327EF61E05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FE4C97-5F8D-6D46-8EED-5B063F02A0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35920" yWindow="3780" windowWidth="27640" windowHeight="16940" xr2:uid="{15501CB9-9377-134A-A4EA-E637D4B0B337}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{15501CB9-9377-134A-A4EA-E637D4B0B337}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="764">
   <si>
     <t>Canonical Name</t>
   </si>
@@ -1572,13 +1572,769 @@
   </si>
   <si>
     <t>pet vmat2 imaging([¹¹c]-dtbz)</t>
+  </si>
+  <si>
+    <t>acetic anhydride / sulfuric acid stain</t>
+  </si>
+  <si>
+    <t>acetic anhydride; acetic anhydride stain; acetic anhydride sulfuric acid stain; acetic-anhydride-sulfuric-acid-stain; acid stain; sulfuric acid stain</t>
+  </si>
+  <si>
+    <t>adipophilin immunostaining</t>
+  </si>
+  <si>
+    <t>adipophilin immunostaining; adipophilin-immunostaining</t>
+  </si>
+  <si>
+    <t>alcian blue</t>
+  </si>
+  <si>
+    <t>alcian blue; alcian-blue</t>
+  </si>
+  <si>
+    <t>ammoniacal carmine</t>
+  </si>
+  <si>
+    <t>ammoniacal carmine; ammoniacal-carmine</t>
+  </si>
+  <si>
+    <t>antibody-patterned polyacrylamide blot region</t>
+  </si>
+  <si>
+    <t>antibody-patterned polyacrylamide blot region; antibody-patterned-polyacrylamide-blot-region; blot region; patterned polyacrylamide blot region antibody</t>
+  </si>
+  <si>
+    <t>apoptosis - caspase-3</t>
+  </si>
+  <si>
+    <t>- caspase-3; 3 caspase apoptosis; apoptosis - caspase-3; apoptosis---caspase-3</t>
+  </si>
+  <si>
+    <t>app accumulation</t>
+  </si>
+  <si>
+    <t>app accumulation; app-accumulation</t>
+  </si>
+  <si>
+    <t>auramine-rhodamine fluorescent stain</t>
+  </si>
+  <si>
+    <t>auramine-rhodamine fluorescent stain; auramine-rhodamine-fluorescent-stain; fluorescent stain; rhodamine fluorescent stain auramine</t>
+  </si>
+  <si>
+    <t>auramine–rhodamine stain</t>
+  </si>
+  <si>
+    <t>auramine rhodamine stain; auramine-rhodamine-stain; rhodamine stain</t>
+  </si>
+  <si>
+    <t>autophagy - lc3/atg</t>
+  </si>
+  <si>
+    <t>atg stain; autophagy - lc3; autophagy - lc3 atg; autophagy - lc3 stain; autophagy---lc3-atg; lc3 atg; lc3/atg autophagy</t>
+  </si>
+  <si>
+    <t>axonal degeneration (btbi)</t>
+  </si>
+  <si>
+    <t>axonal degeneration; axonal-degeneration</t>
+  </si>
+  <si>
+    <t>axonal injury</t>
+  </si>
+  <si>
+    <t>axonal injury; axonal-injury</t>
+  </si>
+  <si>
+    <t>bouin’s fluid</t>
+  </si>
+  <si>
+    <t>bouin’s fluid; bouin’s-fluid</t>
+  </si>
+  <si>
+    <t>brainsmapi</t>
+  </si>
+  <si>
+    <t>capillary electrophoresis</t>
+  </si>
+  <si>
+    <t>capillary electrophoresis; capillary-electrophoresis</t>
+  </si>
+  <si>
+    <t>carbolfuchsin</t>
+  </si>
+  <si>
+    <t>cell death - patterns (tunel/hoechst)</t>
+  </si>
+  <si>
+    <t>- patterns; cell death - patterns; cell death - patterns tunel; cell death - patterns tunel stain; cell-death---patterns; hoechst; hoechst stain; patterns (tunel/hoechst) cell death</t>
+  </si>
+  <si>
+    <t>cerebrovascular histopathology</t>
+  </si>
+  <si>
+    <t>cerebrovascular histopathology; cerebrovascular-histopathology</t>
+  </si>
+  <si>
+    <t>clearmap</t>
+  </si>
+  <si>
+    <t>congo red</t>
+  </si>
+  <si>
+    <t>congo red; congo-red</t>
+  </si>
+  <si>
+    <t>crystal violet</t>
+  </si>
+  <si>
+    <t>crystal violet; crystal-violet</t>
+  </si>
+  <si>
+    <t>cytokine profiling - il-1β, tnfα, il-10</t>
+  </si>
+  <si>
+    <t>10 1β, tnfα, il il cytokine profiling; cytokine profiling - il-1β, tnfα, il-10; cytokine-profiling---il-1β,-tnfα,-il-10; tnfα, il-10</t>
+  </si>
+  <si>
+    <t>electron microscopy</t>
+  </si>
+  <si>
+    <t>electron microscopy; electron-microscopy</t>
+  </si>
+  <si>
+    <t>en face aortic staining</t>
+  </si>
+  <si>
+    <t>aortic staining; en face aortic staining; en-face-aortic-staining</t>
+  </si>
+  <si>
+    <t>endospore stain</t>
+  </si>
+  <si>
+    <t>endospore stain; endospore-stain</t>
+  </si>
+  <si>
+    <t>endospore stain - dorner method</t>
+  </si>
+  <si>
+    <t>dorner method; dorner method endospore stain; endospore stain - dorner method; endospore-stain---dorner-method</t>
+  </si>
+  <si>
+    <t>endospore stain - schaeffer-fulton method</t>
+  </si>
+  <si>
+    <t>endospore stain - schaeffer-fulton method; endospore-stain---schaeffer-fulton-method; fulton method schaeffer endospore stain; schaeffer-fulton method</t>
+  </si>
+  <si>
+    <t>enzyme histochemistry</t>
+  </si>
+  <si>
+    <t>enzyme histochemistry; enzyme-histochemistry</t>
+  </si>
+  <si>
+    <t>eosin</t>
+  </si>
+  <si>
+    <t>flow cytometry</t>
+  </si>
+  <si>
+    <t>flow cytometry; flow-cytometry</t>
+  </si>
+  <si>
+    <t>fluorescence in situ hybridization (fish)</t>
+  </si>
+  <si>
+    <t>fluorescence in situ hybridization; fluorescence-in-situ-hybridization; situ hybridization</t>
+  </si>
+  <si>
+    <t>formalin</t>
+  </si>
+  <si>
+    <t>freezing</t>
+  </si>
+  <si>
+    <t>frozen section</t>
+  </si>
+  <si>
+    <t>frozen section; frozen-section</t>
+  </si>
+  <si>
+    <t>giemsa stain</t>
+  </si>
+  <si>
+    <t>giemsa stain; giemsa-stain</t>
+  </si>
+  <si>
+    <t>glutaraldehyde</t>
+  </si>
+  <si>
+    <t>gram stain</t>
+  </si>
+  <si>
+    <t>gram stain; gram-stain</t>
+  </si>
+  <si>
+    <t>gram’s iodine</t>
+  </si>
+  <si>
+    <t>gram’s iodine; gram’s-iodine</t>
+  </si>
+  <si>
+    <t>grocott-gomori methenamine silver (gms)</t>
+  </si>
+  <si>
+    <t>gomori methenamine silver (gms) grocott; grocott-gomori methenamine silver; grocott-gomori-methenamine-silver; methenamine silver</t>
+  </si>
+  <si>
+    <t>hematoxylin</t>
+  </si>
+  <si>
+    <t>hematoxylin &amp; eosin</t>
+  </si>
+  <si>
+    <t>&amp; eosin; hematoxylin &amp; eosin; hematoxylin-&amp;-eosin</t>
+  </si>
+  <si>
+    <t>immunoassay</t>
+  </si>
+  <si>
+    <t>immunohistochemistry (ihc)</t>
+  </si>
+  <si>
+    <t>immunohistochemistry</t>
+  </si>
+  <si>
+    <t>indigo</t>
+  </si>
+  <si>
+    <t>light microscopy</t>
+  </si>
+  <si>
+    <t>light microscopy; light-microscopy</t>
+  </si>
+  <si>
+    <t>madder</t>
+  </si>
+  <si>
+    <t>malachite green</t>
+  </si>
+  <si>
+    <t>malachite green; malachite-green</t>
+  </si>
+  <si>
+    <t>maldi-ms coupling</t>
+  </si>
+  <si>
+    <t>maldi-ms coupling; maldi-ms-coupling; ms coupling maldi</t>
+  </si>
+  <si>
+    <t>masson’s trichrome</t>
+  </si>
+  <si>
+    <t>masson’s trichrome; masson’s-trichrome</t>
+  </si>
+  <si>
+    <t>mauveine</t>
+  </si>
+  <si>
+    <t>methylene blue</t>
+  </si>
+  <si>
+    <t>methylene blue; methylene-blue</t>
+  </si>
+  <si>
+    <t>mif-related protein 8 elevation</t>
+  </si>
+  <si>
+    <t>8 elevation; mif-related protein 8 elevation; mif-related-protein-8-elevation; related protein 8 elevation mif</t>
+  </si>
+  <si>
+    <t>mucicarmine</t>
+  </si>
+  <si>
+    <t>myelin integrity</t>
+  </si>
+  <si>
+    <t>myelin integrity; myelin-integrity</t>
+  </si>
+  <si>
+    <t>myelin loss - luxol fast blue/mbp ihc (btbi)</t>
+  </si>
+  <si>
+    <t>luxol fast blue/mbp ihc (btbi) myelin loss; mbp ihc; mbp ihc btbi; mbp ihc btbi stain; myelin loss - luxol fast blue; myelin loss - luxol fast blue mbp ihc; myelin loss - luxol fast blue stain; myelin-loss---luxol-fast-blue-mbp-ihc</t>
+  </si>
+  <si>
+    <t>necrosis - h&amp;e</t>
+  </si>
+  <si>
+    <t>- h&amp;e; h&amp;e necrosis; necrosis - h&amp;e; necrosis---h&amp;e</t>
+  </si>
+  <si>
+    <t>neurogenesis - brdu/ki67/dcx</t>
+  </si>
+  <si>
+    <t>brdu/ki67/dcx neurogenesis; dcx stain; ki67; ki67 dcx; ki67 stain; neurogenesis - brdu; neurogenesis - brdu ki67 dcx; neurogenesis - brdu stain; neurogenesis---brdu-ki67-dcx</t>
+  </si>
+  <si>
+    <t>nigrosin</t>
+  </si>
+  <si>
+    <t>nissl stain</t>
+  </si>
+  <si>
+    <t>nissl stain; nissl-stain</t>
+  </si>
+  <si>
+    <t>oil red o</t>
+  </si>
+  <si>
+    <t>oil red o; oil-red-o; red o</t>
+  </si>
+  <si>
+    <t>osmium tetroxide</t>
+  </si>
+  <si>
+    <t>osmium tetroxide; osmium-tetroxide</t>
+  </si>
+  <si>
+    <t>papanicolaou stain</t>
+  </si>
+  <si>
+    <t>papanicolaou stain; papanicolaou-stain</t>
+  </si>
+  <si>
+    <t>paraformaldehyde</t>
+  </si>
+  <si>
+    <t>perfusion</t>
+  </si>
+  <si>
+    <t>periodic acid-schiff (pas)</t>
+  </si>
+  <si>
+    <t>periodic acid-schiff; periodic-acid-schiff; schiff (pas) periodic acid</t>
+  </si>
+  <si>
+    <t>periodic acid–schiff</t>
+  </si>
+  <si>
+    <t>acid schiff; periodic acid schiff; periodic-acid-schiff</t>
+  </si>
+  <si>
+    <t>photoactivated cross-linking</t>
+  </si>
+  <si>
+    <t>linking photoactivated cross; photoactivated cross-linking; photoactivated-cross-linking</t>
+  </si>
+  <si>
+    <t>picric acid</t>
+  </si>
+  <si>
+    <t>picric acid; picric-acid</t>
+  </si>
+  <si>
+    <t>pinched injection</t>
+  </si>
+  <si>
+    <t>pinched injection; pinched-injection</t>
+  </si>
+  <si>
+    <t>polarizing microscopy</t>
+  </si>
+  <si>
+    <t>polarizing microscopy; polarizing-microscopy</t>
+  </si>
+  <si>
+    <t>prussian blue</t>
+  </si>
+  <si>
+    <t>prussian blue; prussian-blue</t>
+  </si>
+  <si>
+    <t>pvdf membrane</t>
+  </si>
+  <si>
+    <t>pvdf membrane; pvdf-membrane</t>
+  </si>
+  <si>
+    <t>saffron</t>
+  </si>
+  <si>
+    <t>safranin</t>
+  </si>
+  <si>
+    <t>sds-protein complex</t>
+  </si>
+  <si>
+    <t>protein complex sds; sds-protein complex; sds-protein-complex</t>
+  </si>
+  <si>
+    <t>sheath-flow interface</t>
+  </si>
+  <si>
+    <t>flow interface sheath; sheath-flow interface; sheath-flow-interface</t>
+  </si>
+  <si>
+    <t>silver nitrate stain</t>
+  </si>
+  <si>
+    <t>nitrate stain; silver nitrate stain; silver-nitrate-stain</t>
+  </si>
+  <si>
+    <t>silver stain</t>
+  </si>
+  <si>
+    <t>silver stain; silver-stain</t>
+  </si>
+  <si>
+    <t>sirius red</t>
+  </si>
+  <si>
+    <t>sirius red; sirius-red</t>
+  </si>
+  <si>
+    <t>succinate dehydrogenase</t>
+  </si>
+  <si>
+    <t>succinate dehydrogenase; succinate-dehydrogenase</t>
+  </si>
+  <si>
+    <t>sudan black</t>
+  </si>
+  <si>
+    <t>sudan black; sudan-black</t>
+  </si>
+  <si>
+    <t>telepathology (digital slide sharing)</t>
+  </si>
+  <si>
+    <t>telepathology</t>
+  </si>
+  <si>
+    <t>tetrachrome (alcian blue + pas + hematoxylin + picric acid)</t>
+  </si>
+  <si>
+    <t>tetrachrome</t>
+  </si>
+  <si>
+    <t>vascular tortuosity</t>
+  </si>
+  <si>
+    <t>vascular tortuosity; vascular-tortuosity</t>
+  </si>
+  <si>
+    <t>vasculogenesis - vegf ihc (btbi)</t>
+  </si>
+  <si>
+    <t>vasculogenesis - vegf ihc; vasculogenesis---vegf-ihc; vegf ihc; vegf ihc (btbi) vasculogenesis</t>
+  </si>
+  <si>
+    <t>western blot</t>
+  </si>
+  <si>
+    <t>western blot; western-blot</t>
+  </si>
+  <si>
+    <t>white-matter degeneration (btbi)</t>
+  </si>
+  <si>
+    <t>matter degeneration (btbi) white; white-matter degeneration; white-matter-degeneration</t>
+  </si>
+  <si>
+    <t>ziehl-neelsen (acid-fast) stain</t>
+  </si>
+  <si>
+    <t>fast) stain neelsen (acid ziehl; ziehl-neelsen stain; ziehl-neelsen-stain</t>
+  </si>
+  <si>
+    <t>aggression test</t>
+  </si>
+  <si>
+    <t>aggression test; aggression assessment; aggression check; hostile behavior evaluation; aggressive response test</t>
+  </si>
+  <si>
+    <t>body weight measurement</t>
+  </si>
+  <si>
+    <t>body weight check; body weight measurement; body weight monitoring; weighing procedure; weighing record; weighing session; weight tracking</t>
+  </si>
+  <si>
+    <t>circular locomotion test</t>
+  </si>
+  <si>
+    <t>circular locomotion test; circular locomotion assessment; circular locomotion tracking; rotational movement observation; spinning behavior test</t>
+  </si>
+  <si>
+    <t>clinical welfare scoring</t>
+  </si>
+  <si>
+    <t>clinical welfare score; clinical welfare assessment; clinical welfare rating; animal welfare evaluation; welfare condition scoring</t>
+  </si>
+  <si>
+    <t>forelimb flexion test</t>
+  </si>
+  <si>
+    <t>gentle push response</t>
+  </si>
+  <si>
+    <t>gentle push test; gentle push reaction; gentle push response; nudging response; push induced reaction</t>
+  </si>
+  <si>
+    <t>grooming score</t>
+  </si>
+  <si>
+    <t>grooming score; grooming rating; grooming assessment; self grooming behavior; grooming activity evaluation</t>
+  </si>
+  <si>
+    <t>home-cage activity observation</t>
+  </si>
+  <si>
+    <t>home cage activity monitoring; home cage activity observation; home cage activity tracking; in cage activity check; in cage activity evaluation; in cage activity observation</t>
+  </si>
+  <si>
+    <t>home-cage wheel running (optional)</t>
+  </si>
+  <si>
+    <t>home cage wheel running; home cage wheel activity; voluntary running wheel monitoring; voluntary running wheel usage; in cage wheel movement</t>
+  </si>
+  <si>
+    <t>isolation behavior</t>
+  </si>
+  <si>
+    <t>isolation behavior; isolation response; isolation symptoms; social withdrawal; loneliness signs</t>
+  </si>
+  <si>
+    <t>seizure monitoring</t>
+  </si>
+  <si>
+    <t>seizure monitoring; seizure observation; seizure tracking; epileptic activity monitoring; convulsion check</t>
+  </si>
+  <si>
+    <t>forelimb flexion test; forelimb extension test; limb movement; limb reflex assessment; paw response test</t>
+  </si>
+  <si>
+    <t>rectal temperature</t>
+  </si>
+  <si>
+    <t>rectal temperature; rectal temp; rec-temp reading; rectal thermometer reading</t>
+  </si>
+  <si>
+    <t>infrared thermography</t>
+  </si>
+  <si>
+    <t>infrared thermography; infrared thermal imaging; ir thermography; thermal imaging</t>
+  </si>
+  <si>
+    <t>flank movement count</t>
+  </si>
+  <si>
+    <t>flank movement count; flank movement tally; flank motions count; flank motion measurement</t>
+  </si>
+  <si>
+    <t>blood glucose assay</t>
+  </si>
+  <si>
+    <t>blood glucose assay; blood sugar assay; glucose blood test; bg measurement</t>
+  </si>
+  <si>
+    <t>cortisol elisa</t>
+  </si>
+  <si>
+    <t>cortisol elisa; cortisol enzyme-linked immunosorbent assay; cortisol immunoassay; serum cortisol elisa</t>
+  </si>
+  <si>
+    <t>ileum integrity assessment</t>
+  </si>
+  <si>
+    <t>ileum integrity assessment; ileal integrity evaluation; small intestine integrity assessment; ileum barrier check</t>
+  </si>
+  <si>
+    <t>proteomics profiling</t>
+  </si>
+  <si>
+    <t>proteomics profiling; protein profiling; proteome analysis; proteomic analysis</t>
+  </si>
+  <si>
+    <t>temperature-humidity index (thi)</t>
+  </si>
+  <si>
+    <t>temperature-humidity index; thi; heat stress index; temp–humidity indicator</t>
+  </si>
+  <si>
+    <t>scan sampling &amp; video ethogram</t>
+  </si>
+  <si>
+    <t>scan sampling &amp; video ethogram; scan sampling and video ethogram; behavioral video ethogram; scan-video ethogram</t>
+  </si>
+  <si>
+    <t>acoustic vocalization</t>
+  </si>
+  <si>
+    <t>acoustic vocalization; audio vocalization; sound vocalization; acoustic call analysis</t>
+  </si>
+  <si>
+    <t>direct observation of social interactions</t>
+  </si>
+  <si>
+    <t>direct observation of social interactions; live social behavior observation; direct behavior observation; social scan</t>
+  </si>
+  <si>
+    <t>body lesion scoring</t>
+  </si>
+  <si>
+    <t>body lesion scoring; body lesion score; lesion scoring on body; cutaneous lesion scoring</t>
+  </si>
+  <si>
+    <t>tail lesion scoring</t>
+  </si>
+  <si>
+    <t>tail lesion scoring; tail lesion score; lesion scoring on tail; tail injury scoring</t>
+  </si>
+  <si>
+    <t>weight gain measurement</t>
+  </si>
+  <si>
+    <t>weight gain measurement; weight gain tracking; body weight gain; weight increment measurement</t>
+  </si>
+  <si>
+    <t>blood cortisol assay</t>
+  </si>
+  <si>
+    <t>blood cortisol assay; blood cortisol measurement; cortisol blood test; plasma cortisol assay</t>
+  </si>
+  <si>
+    <t>salivary cortisol assay</t>
+  </si>
+  <si>
+    <t>salivary cortisol assay; saliva cortisol test; salivary cortisol measurement; cortisol salivary assay</t>
+  </si>
+  <si>
+    <t>blood lactate assay</t>
+  </si>
+  <si>
+    <t>blood lactate assay; blood lactate measurement; lactate blood test; lactate assay</t>
+  </si>
+  <si>
+    <t>blood catecholamine assay</t>
+  </si>
+  <si>
+    <t>blood catecholamine assay; catecholamine blood test; catecholamine measurement; plasma catecholamine assay</t>
+  </si>
+  <si>
+    <t>blood acth assay</t>
+  </si>
+  <si>
+    <t>blood acth assay; acth blood test; adrenocorticotropic hormone assay; acth plasma assay</t>
+  </si>
+  <si>
+    <t>blood haptoglobin assay</t>
+  </si>
+  <si>
+    <t>blood haptoglobin assay; haptoglobin blood test; plasma haptoglobin measurement; haptoglobin assay</t>
+  </si>
+  <si>
+    <t>average daily weight gain</t>
+  </si>
+  <si>
+    <t>average daily weight gain; average daily gain; adg; daily weight gain average</t>
+  </si>
+  <si>
+    <t>feed intake</t>
+  </si>
+  <si>
+    <t>feed intake; feed consumption; feed intake measurement; feed consumption rate</t>
+  </si>
+  <si>
+    <t>feed conversion rate</t>
+  </si>
+  <si>
+    <t>feed conversion rate; feed conversion ratio; fcr; feed efficiency ratio</t>
+  </si>
+  <si>
+    <t>body temperature</t>
+  </si>
+  <si>
+    <t>body temperature; core body temperature; internal temperature; body temp</t>
+  </si>
+  <si>
+    <t>organ integrity assessment</t>
+  </si>
+  <si>
+    <t>organ integrity assessment; organ integrity evaluation; organ health assessment; organ integrity check</t>
+  </si>
+  <si>
+    <t>respiratory rate</t>
+  </si>
+  <si>
+    <t>respiratory rate; respiration rate; breaths per minute; respiratory frequency</t>
+  </si>
+  <si>
+    <t>diarrhea severity scoring</t>
+  </si>
+  <si>
+    <t>diarrhea severity scoring; diarrhea severity score; stool consistency scoring; fecal scoring</t>
+  </si>
+  <si>
+    <t>viral load quantification</t>
+  </si>
+  <si>
+    <t>viral load quantification; viral load measurement; viral titer quantification; virus quantification</t>
+  </si>
+  <si>
+    <t>cytokine concentration assay</t>
+  </si>
+  <si>
+    <t>cytokine concentration assay; cytokine measurement; cytokine level assay; cytokine quantitation</t>
+  </si>
+  <si>
+    <t>interleukin gene/protein analysis</t>
+  </si>
+  <si>
+    <t>interleukin gene/protein analysis; il gene/protein analysis; interleukin expression analysis; il profiling</t>
+  </si>
+  <si>
+    <t>immunoglobulin assay</t>
+  </si>
+  <si>
+    <t>immunoglobulin assay; antibody assay; immunoglobulin measurement; immunoassay</t>
+  </si>
+  <si>
+    <t>acute-phase protein assay</t>
+  </si>
+  <si>
+    <t>acute-phase protein assay; acute phase protein measurement; app assay; acute reactant assay</t>
+  </si>
+  <si>
+    <t>hematology panel</t>
+  </si>
+  <si>
+    <t>hematology panel; complete blood count; blood count panel; hematological profile</t>
+  </si>
+  <si>
+    <t>depression-like behavior scoring</t>
+  </si>
+  <si>
+    <t>depression-like behavior scoring; depression-like behavior score; behavioral despair scoring; depressive behavior assessment</t>
+  </si>
+  <si>
+    <t>fluorescence imaging</t>
+  </si>
+  <si>
+    <t>fluorescence imaging; fluorescent imaging; fluorescence-based imaging; fluorescence microscopy; fluorescent microscopy; fluorescence-microscopy; optical fluorescence imaging; optical-fluorescence imaging; intrinsic fluorescence imaging; intrinsic-fluorescence imaging; fluorescence-imaging; fluorescence / imaging; fluoro imaging;</t>
+  </si>
+  <si>
+    <t>computed tomography</t>
+  </si>
+  <si>
+    <t>computed tomography; CT scan; CAT scan; CT imaging; CT image; CT images; X-ray computed tomography; X-ray CT; axial CT; spiral CT; helical CT; multi-detector CT; multidetector CT; MDCT; MSCT; fan-beam CT; cone-beam CT; high-resolution CT; HRCT; diagnostic CT scan; CT slice; CT slices</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1599,6 +2355,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1621,10 +2383,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1959,11 +2722,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F7C088-4AE2-FE43-98E3-B1584DF0C0CC}">
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="82.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -4014,6 +4777,1086 @@
         <v>468</v>
       </c>
     </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>512</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>514</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>516</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>518</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>520</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>522</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>524</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>526</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>528</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>530</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>532</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>534</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>536</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>538</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>539</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>541</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>542</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>544</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>546</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>547</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>549</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>551</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>553</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>555</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>557</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>559</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>561</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>563</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>565</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>566</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>568</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>570</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>571</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>572</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>574</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>576</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>577</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>579</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>581</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>583</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>584</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>586</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>587</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>589</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>590</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>592</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>593</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>595</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>597</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>599</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>600</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>602</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>604</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>605</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>607</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>609</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" t="s">
+        <v>611</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" t="s">
+        <v>613</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" t="s">
+        <v>614</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" t="s">
+        <v>616</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" t="s">
+        <v>618</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" t="s">
+        <v>620</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" t="s">
+        <v>622</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
+        <v>623</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321" t="s">
+        <v>624</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322" t="s">
+        <v>626</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323" t="s">
+        <v>628</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324" t="s">
+        <v>630</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325" t="s">
+        <v>632</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326" t="s">
+        <v>634</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327" t="s">
+        <v>636</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A328" t="s">
+        <v>638</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A329" t="s">
+        <v>640</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A330" t="s">
+        <v>641</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A331" t="s">
+        <v>642</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>644</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A333" t="s">
+        <v>646</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A334" t="s">
+        <v>648</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A335" t="s">
+        <v>650</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A336" t="s">
+        <v>652</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>654</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>656</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>658</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>660</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>662</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>664</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>666</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>668</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A345" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B345" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A346" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A347" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A348" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A349" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A350" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A351" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A352" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A353" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356" t="s">
+        <v>692</v>
+      </c>
+      <c r="B356" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357" t="s">
+        <v>694</v>
+      </c>
+      <c r="B357" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A358" t="s">
+        <v>696</v>
+      </c>
+      <c r="B358" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359" t="s">
+        <v>698</v>
+      </c>
+      <c r="B359" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A360" t="s">
+        <v>700</v>
+      </c>
+      <c r="B360" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A361" t="s">
+        <v>702</v>
+      </c>
+      <c r="B361" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A362" t="s">
+        <v>704</v>
+      </c>
+      <c r="B362" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A363" t="s">
+        <v>706</v>
+      </c>
+      <c r="B363" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
+        <v>708</v>
+      </c>
+      <c r="B364" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365" t="s">
+        <v>710</v>
+      </c>
+      <c r="B365" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366" t="s">
+        <v>712</v>
+      </c>
+      <c r="B366" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
+        <v>714</v>
+      </c>
+      <c r="B367" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
+        <v>716</v>
+      </c>
+      <c r="B368" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369" t="s">
+        <v>718</v>
+      </c>
+      <c r="B369" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370" t="s">
+        <v>720</v>
+      </c>
+      <c r="B370" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371" t="s">
+        <v>722</v>
+      </c>
+      <c r="B371" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372" t="s">
+        <v>724</v>
+      </c>
+      <c r="B372" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A373" t="s">
+        <v>726</v>
+      </c>
+      <c r="B373" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374" t="s">
+        <v>728</v>
+      </c>
+      <c r="B374" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375" t="s">
+        <v>730</v>
+      </c>
+      <c r="B375" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376" t="s">
+        <v>732</v>
+      </c>
+      <c r="B376" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377" t="s">
+        <v>734</v>
+      </c>
+      <c r="B377" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
+        <v>736</v>
+      </c>
+      <c r="B378" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>738</v>
+      </c>
+      <c r="B379" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>740</v>
+      </c>
+      <c r="B380" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>742</v>
+      </c>
+      <c r="B381" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>744</v>
+      </c>
+      <c r="B382" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>746</v>
+      </c>
+      <c r="B383" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>748</v>
+      </c>
+      <c r="B384" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>750</v>
+      </c>
+      <c r="B385" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>752</v>
+      </c>
+      <c r="B386" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>754</v>
+      </c>
+      <c r="B387" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>756</v>
+      </c>
+      <c r="B388" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>758</v>
+      </c>
+      <c r="B389" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>760</v>
+      </c>
+      <c r="B390" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>762</v>
+      </c>
+      <c r="B391" t="s">
+        <v>763</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/03_IE_tasks/data/related/outcomes_endpoints/harmonized_synonyms_GPT.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/harmonized_synonyms_GPT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FE4C97-5F8D-6D46-8EED-5B063F02A0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F6706C-74F0-FA4C-BF90-5C7D8F752AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{15501CB9-9377-134A-A4EA-E637D4B0B337}"/>
+    <workbookView xWindow="51000" yWindow="7740" windowWidth="30240" windowHeight="17740" xr2:uid="{15501CB9-9377-134A-A4EA-E637D4B0B337}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="1042">
   <si>
     <t>Canonical Name</t>
   </si>
@@ -284,12 +284,6 @@
     <t>confocal microscopy; laser-scanning confocal imaging</t>
   </si>
   <si>
-    <t>contextual fear conditioning</t>
-  </si>
-  <si>
-    <t>contextual FC; context-fear conditioning</t>
-  </si>
-  <si>
     <t>continuous performance test (rodent CPT)</t>
   </si>
   <si>
@@ -320,12 +314,6 @@
     <t>CubicCloud imaging pipeline; 3D cloud reconstruction method</t>
   </si>
   <si>
-    <t>cued fear conditioning</t>
-  </si>
-  <si>
-    <t>cued FC; tone-fear conditioning</t>
-  </si>
-  <si>
     <t>cylinder test</t>
   </si>
   <si>
@@ -401,9 +389,6 @@
     <t>electroencephalography (eeg)</t>
   </si>
   <si>
-    <t>EEG recording; electrical brain activity recording</t>
-  </si>
-  <si>
     <t>electronic von frey</t>
   </si>
   <si>
@@ -467,9 +452,6 @@
     <t>fear conditioning test</t>
   </si>
   <si>
-    <t>FC test; conditioned fear assay</t>
-  </si>
-  <si>
     <t>fecal corticosterone metabolites (fcms)</t>
   </si>
   <si>
@@ -2033,9 +2015,6 @@
     <t>western blot</t>
   </si>
   <si>
-    <t>western blot; western-blot</t>
-  </si>
-  <si>
     <t>white-matter degeneration (btbi)</t>
   </si>
   <si>
@@ -2328,6 +2307,861 @@
   </si>
   <si>
     <t>computed tomography; CT scan; CAT scan; CT imaging; CT image; CT images; X-ray computed tomography; X-ray CT; axial CT; spiral CT; helical CT; multi-detector CT; multidetector CT; MDCT; MSCT; fan-beam CT; cone-beam CT; high-resolution CT; HRCT; diagnostic CT scan; CT slice; CT slices</t>
+  </si>
+  <si>
+    <t>pathme viewer</t>
+  </si>
+  <si>
+    <t>PathMe Viewer; PathMe visualizer; PathMe Web Viewer; PathMe exploration tool; pathme-viewer; PathMe UI; PathMe interface; PathMe pathway viewer</t>
+  </si>
+  <si>
+    <t>pathwaycommons</t>
+  </si>
+  <si>
+    <t>Pathway Commons; PathwayCommons; PC database; Pathway Commons resource; pathway-commons; PathwayCommons API; PC web portal; PathwayCommons knowledgebase</t>
+  </si>
+  <si>
+    <t>phosphoproteomics</t>
+  </si>
+  <si>
+    <t>phosphoproteomics; phospho-proteomics; phospho proteomics; phosphoproteome profiling; phosphoproteome analysis; phospho-peptidomics; global phosphoproteomics; site-specific phosphoproteomics</t>
+  </si>
+  <si>
+    <t>protein microarray</t>
+  </si>
+  <si>
+    <t>protein microarray; protein array; protein-chip; proteome microarray; high-density protein array; protein macroarray; protein-microarray platform</t>
+  </si>
+  <si>
+    <t>qrt-pcr array</t>
+  </si>
+  <si>
+    <t>qRT-PCR array; qRT PCR array; quantitative real-time PCR array; qPCR array; realtime PCR array; qRT-PCR panel; quantitative RT-PCR array</t>
+  </si>
+  <si>
+    <t>recon3d</t>
+  </si>
+  <si>
+    <t>Recon 3D; Recon3D; Recon-3D; Recon 3D metabolic model; Recon3D genome-scale model; Recon3D reconstruction; Recon-3D network</t>
+  </si>
+  <si>
+    <t>reverse-phase protein microarray</t>
+  </si>
+  <si>
+    <t>reverse-phase protein array; RPPA; RPPA microarray; reverse phase protein microarray; reverse-phase protein-array platform; RPPA profiling; reverse-phase proteome array</t>
+  </si>
+  <si>
+    <t>rna-seq</t>
+  </si>
+  <si>
+    <t>sequence assembly</t>
+  </si>
+  <si>
+    <t>sequence assembly; genome assembly; de novo assembly; assembly pipeline; sequence assembler; contig assembly; scaffold assembly</t>
+  </si>
+  <si>
+    <t>shotgun metagenomics</t>
+  </si>
+  <si>
+    <t>shotgun metagenomics; shotgun metagenomic sequencing; metagenomic shotgun sequencing; WGS metagenomics; whole-genome shotgun metagenomics; untargeted metagenomics</t>
+  </si>
+  <si>
+    <t>single-cell chip-seq</t>
+  </si>
+  <si>
+    <t>single-cell ChIP-seq; scChIP-seq; single cell ChIP-seq; single-cell chromatin immunoprecipitation sequencing; single-cell ChIP sequencing; single-cell ChIP-Seq assay</t>
+  </si>
+  <si>
+    <t>single-cell proteomics</t>
+  </si>
+  <si>
+    <t>single-cell proteomics; scProteomics; single cell proteomics; single-cell mass spec proteomics; single-cell protein profiling; proteomic single-cell analysis; sc protein quantification</t>
+  </si>
+  <si>
+    <t>acetylomics</t>
+  </si>
+  <si>
+    <t>acetylomics; acetyl-proteomics; lysine acetylome profiling; global acetylome analysis; protein acetylation profiling</t>
+  </si>
+  <si>
+    <t>affinity proteomics</t>
+  </si>
+  <si>
+    <t>affinity proteomics; affinity-based proteomics; antibody-based proteomics; pull-down proteomics; affinity purification mass spectrometry; AP-MS</t>
+  </si>
+  <si>
+    <t>biocyc</t>
+  </si>
+  <si>
+    <t>BioCyc; BioCyc database; BioCyc Pathway Tools; BioCyc collection; BioCyc PGDB; BioCyc knowledge base</t>
+  </si>
+  <si>
+    <t>cell sorting</t>
+  </si>
+  <si>
+    <t>cell sorting; cell-sorting; fluorescence-activated cell sorting; FACS; magnetic-activated cell sorting; MACS; flow-cytometry sorting</t>
+  </si>
+  <si>
+    <t>ChIP-seq (histone modifications)</t>
+  </si>
+  <si>
+    <t>ChIP-seq (histone marks); ChIPseq for histones; ChIP-Seq histone modification profiling; histone ChIP-seq; epi-ChIP-seq; chromatin immunoprecipitation sequencing (histone)</t>
+  </si>
+  <si>
+    <t>circRNA-seq</t>
+  </si>
+  <si>
+    <t>circRNA-seq; circRNA sequencing; circular RNA-seq; circ-seq; circular RNA sequencing; circRNA transcriptome profiling</t>
+  </si>
+  <si>
+    <t>cypath2a</t>
+  </si>
+  <si>
+    <t>CyPath2A; CYPATH2A; CyPath 2A; CYPATH version 2a; CyPath2A tool; CYPATH2A pathway analysis</t>
+  </si>
+  <si>
+    <t>density gradient centrifugation</t>
+  </si>
+  <si>
+    <t>density gradient centrifugation; density-gradient centrifugation; gradient centrifugation; sucrose gradient centrifugation; Percoll gradient centrifugation; rate-zonal centrifugation; equilibrium density centrifugation</t>
+  </si>
+  <si>
+    <t>exome sequencing</t>
+  </si>
+  <si>
+    <t>exome sequencing; whole-exome sequencing; WES; whole exome sequencing; exome capture sequencing; targeted exome sequencing</t>
+  </si>
+  <si>
+    <t>genome annotation</t>
+  </si>
+  <si>
+    <t>genome annotation; gene annotation; structural genome annotation; functional genome annotation; genome feature annotation</t>
+  </si>
+  <si>
+    <t>genome-wide association study (GWAS)</t>
+  </si>
+  <si>
+    <t>genome-wide association study; GWAS; GWA study; genome-wide association analysis; GWAS analysis; genome wide association study</t>
+  </si>
+  <si>
+    <t>genotyping array</t>
+  </si>
+  <si>
+    <t>genotyping array; SNP array; SNP genotyping array; DNA microarray; genotyping microarray; high-density genotyping array</t>
+  </si>
+  <si>
+    <t>glycoproteomics</t>
+  </si>
+  <si>
+    <t>glycoproteomics; glyco-proteomics; glycoproteome analysis; glycoproteome profiling; lectin-based proteomics; glycopeptide analysis</t>
+  </si>
+  <si>
+    <t>SLEAP; sleap; SLEAP software; Social LEAP Estimates Animal Poses; SLEAP pose estimation; sleap-tracking; SLEAP tracking</t>
+  </si>
+  <si>
+    <t>social approach test; social approach assays; social interaction test; sociability test; social preference test; three-chamber social approach; social approach paradigm</t>
+  </si>
+  <si>
+    <t>social avoidance test</t>
+  </si>
+  <si>
+    <t>social avoidance test; social withdrawal test; social interaction avoidance assay; avoidance of conspecific test; social fear avoidance test</t>
+  </si>
+  <si>
+    <t>social fear transmission</t>
+  </si>
+  <si>
+    <t>social fear transmission; fear contagion test; observational fear transfer; vicarious fear paradigm; social transmission of fear; fear empathy test</t>
+  </si>
+  <si>
+    <t>social food-preference assay</t>
+  </si>
+  <si>
+    <t>social food-preference assay; social food preference test; two-choice food-preference assay; social feeding preference; pairwise food preference test</t>
+  </si>
+  <si>
+    <t>social instrumental task</t>
+  </si>
+  <si>
+    <t>social instrumental task; social operant task; social lever-pressing assay; social reinforcement learning task; social instrumental conditioning</t>
+  </si>
+  <si>
+    <t>SURF; surf; SURF assay; Social Utilization of Rewards Framework; SURF decision-making task; surf paradigm</t>
+  </si>
+  <si>
+    <t>three-chamber sociability</t>
+  </si>
+  <si>
+    <t>three-chamber sociability test; three-chamber social preference; 3-chamber sociability; three-chamber social interaction; 3-chamber social approach</t>
+  </si>
+  <si>
+    <t>touchscreen IED; intra-extra-dimensional set-shifting; ID/ED set-shift; touchscreen ID/ED task; attentional set-shifting task; IED touchscreen assay</t>
+  </si>
+  <si>
+    <t>trial-unique delayed non-matching-to-location; TUNL; delayed non-matching-to-location test; touchscreen TUNL; TUNL spatial memory task; non-matching location assay</t>
+  </si>
+  <si>
+    <t>tube test</t>
+  </si>
+  <si>
+    <t>tube test; tube dominance test; social tube test; tube-dominance assay; tube-dominance paradigm; dominance tube test</t>
+  </si>
+  <si>
+    <t>two-choice social decision-making</t>
+  </si>
+  <si>
+    <t>two-choice social decision-making; two choice social decision task; 2-choice social decision; social decision-making assay; two-option social choice task; social choice decision-making</t>
+  </si>
+  <si>
+    <t>Vogel conflict test; Vogel punished drinking test; Vogel conflict paradigm; punished-sipper test; Vogel punished drinking assay; anxiety conflict test</t>
+  </si>
+  <si>
+    <t>sleap</t>
+  </si>
+  <si>
+    <t>surf</t>
+  </si>
+  <si>
+    <t>touchscreen intra-/extra-dimensional (ied) set-shifting</t>
+  </si>
+  <si>
+    <t>trial-unique delayed non-matching-to-location (tunl)</t>
+  </si>
+  <si>
+    <t>vogel conflict test</t>
+  </si>
+  <si>
+    <t>keypoint detection</t>
+  </si>
+  <si>
+    <t>keypoint detection; key-point detection; key point detection; landmark detection; keypoint localization; body keypoint detection; skeleton keypoint detection; feature point detection</t>
+  </si>
+  <si>
+    <t>long-term home-cage observation</t>
+  </si>
+  <si>
+    <t>long-term home-cage observation; long term home cage observation; continuous home-cage monitoring; extended home-cage observation; automated home-cage monitoring; unobtrusive home cage monitoring; home-cage behavioral tracking</t>
+  </si>
+  <si>
+    <t>mars</t>
+  </si>
+  <si>
+    <t>mars; mars toolkit; mars platform; mars software; mars framework; mars analysis; mars system</t>
+  </si>
+  <si>
+    <t>moseq</t>
+  </si>
+  <si>
+    <t>moseq; mo-seq; motion sequencing; motion-seq; motion seq; behavior sequencing; unsupervised motion sequencing; behavior motif sequencing</t>
+  </si>
+  <si>
+    <t>non-video (e.g. wifi) pose estimation</t>
+  </si>
+  <si>
+    <t>non-video pose estimation; non video pose estimation; wifi-based pose estimation; rf-based pose estimation; wireless pose estimation; nonvisual pose estimation; radio-frequency pose estimation; sensor-based pose estimation</t>
+  </si>
+  <si>
+    <t>overall neurological function (m)nss</t>
+  </si>
+  <si>
+    <t>overall neurological function (mnss); overall neurological function mnss; mnss; modified neurological severity score; modified neurological severity scale; neurological severity scoring; neurological function mnss; m nss</t>
+  </si>
+  <si>
+    <t>paired-associate learning (pal)</t>
+  </si>
+  <si>
+    <t>paired-associate learning (pal); pal; paired associate learning; paired-associates learning; paired associate memory; pal test; paired-associate memory task; pal paradigm</t>
+  </si>
+  <si>
+    <t>place escape avoidance paradigm (peap)</t>
+  </si>
+  <si>
+    <t>place escape avoidance paradigm (peap); peap; place-escape avoidance paradigm; place escape aversion paradigm; place escape avoidance assay; peap paradigm</t>
+  </si>
+  <si>
+    <t>pose estimation</t>
+  </si>
+  <si>
+    <t>pose estimation; body pose estimation; 2d pose estimation; 3d pose estimation; human pose estimation; animal pose estimation; skeletal pose estimation; kinematic pose estimation</t>
+  </si>
+  <si>
+    <t>randall-selitto test</t>
+  </si>
+  <si>
+    <t>randall-selitto test; randall selitto test; randall-selitto assay; paw pressure test; paw pressure analgesia test; pressure tail flick test</t>
+  </si>
+  <si>
+    <t>re-wilding naturalistic arena</t>
+  </si>
+  <si>
+    <t>re-wilding naturalistic arena; rewilding naturalistic arena; naturalistic rewilding arena; naturalistic arena; re-wilding arena; wild-like arena; rewild arena; naturalistic behavioral arena</t>
+  </si>
+  <si>
+    <t>rotating-pole</t>
+  </si>
+  <si>
+    <t>rotating-pole; rotating pole; rotating-pole test; rotating pole test; rotating-pole apparatus; pole rotation assay</t>
+  </si>
+  <si>
+    <t>acoustic startle response (± ppi)</t>
+  </si>
+  <si>
+    <t>acoustic startle response; acoustic startle reflex; ASR; startle response assay; startle reflex test; prepulse inhibition assay; PPI; acoustic startle with PPI; ASR-PPI test; prepulse inhibition of startle</t>
+  </si>
+  <si>
+    <t>adhesive-removal</t>
+  </si>
+  <si>
+    <t>adhesive-removal test; adhesive removal assay; sticky-tape test; tape removal test; somatosensory neglect test; adhesive-tape removal; adhesive sticker test; sensorimotor tape removal</t>
+  </si>
+  <si>
+    <t>b-soid</t>
+  </si>
+  <si>
+    <t>b-soid; B-SOID; bsoid; BSOID; behavioral segmentation of interacting organisms; B-SOID algorithm; b-soid software; BSOID pipeline; behavior syllable detection; b-soid posture classifier</t>
+  </si>
+  <si>
+    <t>bbb locomotor scale</t>
+  </si>
+  <si>
+    <t>BBB locomotor scale; BBB scale; Basso-Beattie-Bresnahan scale; Basso Beattie Bresnahan locomotor rating; BBB score; BBB rating scale; Basso-Beattie-Bresnahan locomotor scale</t>
+  </si>
+  <si>
+    <t>beam balance</t>
+  </si>
+  <si>
+    <t>beam balance test; balance-beam assay; beam-walking test; narrow beam test; balance beam task; beam walk assay; beam-walk test; beam‐balance performance</t>
+  </si>
+  <si>
+    <t>cereal-eating (ibb) forelimb scale</t>
+  </si>
+  <si>
+    <t>cereal-eating IBB scale; IBB forelimb scale; cereal-eating test; Irvine-Beattie-Bresnahan forelimb scale; food-pellet reaching assay; IBB cereal eating test; forelimb food retrieval scale; IBB reaching scale</t>
+  </si>
+  <si>
+    <t>computational ethology pipeline</t>
+  </si>
+  <si>
+    <t>computational ethology pipeline; ethology analysis pipeline; behavior analysis pipeline; automated ethology workflow; machine-learning ethology pipeline; computational ethology toolkit; behavior-coding pipeline; ethogram automation pipeline</t>
+  </si>
+  <si>
+    <t>continuous performance test (rodent cpt)</t>
+  </si>
+  <si>
+    <t>continuous performance test; rodent CPT; CPT assay; sustained attention task; vigilance test; continuous performance task; rodent vigilance CPT; sustained attention CPT; continuous attention assay</t>
+  </si>
+  <si>
+    <t>cylinder (limb-use asymmetry)</t>
+  </si>
+  <si>
+    <t>cylinder test; cylinder assay; cylinder limb-use test; forelimb asymmetry test; cylinder rearing test; limb-use asymmetry assay; cylinder rearing asymmetry; cylinder placement test</t>
+  </si>
+  <si>
+    <t>deeplabcut (dlc)</t>
+  </si>
+  <si>
+    <t>deeplabcut; DLC; DeepLabCut; deep lab cut; Deep LabCut toolbox; deeplabcut pose estimation; markerless pose estimation (DLC); deeplabcut pipeline; deep-lab-cut software; DLC behavioral tracking</t>
+  </si>
+  <si>
+    <t>bench-top low-field mri</t>
+  </si>
+  <si>
+    <t>bench-top low-field mri; benchtop low-field mri; bench-top low-field magnetic resonance imaging; low-field benchtop mri; table-top low-field mri; portable low-field mri; bench-top mri; benchtop low-field magnetic resonance imaging</t>
+  </si>
+  <si>
+    <t>bioluminescence imaging</t>
+  </si>
+  <si>
+    <t>blood-pool uspio mri</t>
+  </si>
+  <si>
+    <t>blood-pool uspio mri; ultrasmall superparamagnetic iron oxide mri; blood-pool uspio imaging; uspio-enhanced mri; blood-pool iron oxide mri; uspio mri; ultrasmall spio mri</t>
+  </si>
+  <si>
+    <t>bold fmri</t>
+  </si>
+  <si>
+    <t>bold fmri; bold functional mri; blood oxygenation level–dependent mri; fMRI BOLD; bold imaging; functional mri using bold contrast</t>
+  </si>
+  <si>
+    <t>chemogenetics-fmrs</t>
+  </si>
+  <si>
+    <t>chemogenetics-fmrs; chemogenetics fMRS; chemogenetic magnetic resonance spectroscopy; fMRS; functional mrs; chemogenetic mrs; chemogenetics-based spectroscopy</t>
+  </si>
+  <si>
+    <t>co-registered pet/ct</t>
+  </si>
+  <si>
+    <t>co-registered pet/ct; co-registered pet ct; pet/ct fusion; pet ct fusion imaging; fused pet-ct; pet/ct coregistered imaging; coregistered pet-ct; pet-ct co-registration; fused pet/ct</t>
+  </si>
+  <si>
+    <t>co-registered spect/ct</t>
+  </si>
+  <si>
+    <t>co-registered spect/ct; co-registered spect ct; spect/ct fusion; spect ct fusion imaging; fused spect-ct; spect/ct coregistered imaging; coregistered spect-ct; spect-ct co-registration; fused spect/ct</t>
+  </si>
+  <si>
+    <t>contrast-enhanced ct</t>
+  </si>
+  <si>
+    <t>contrast-enhanced ct; contrast ct; ce-ct; ct with contrast; iodinated contrast ct; contrast-enhanced computed tomography; ce ct</t>
+  </si>
+  <si>
+    <t>contrast-enhanced t1-weighted mri</t>
+  </si>
+  <si>
+    <t>contrast-enhanced t1-weighted mri; ce t1 mri; t1-weighted ce-mri; t1w ce-mri; gadolinium-enhanced t1-weighted mri; gadolinium t1 mri; t1-weighted gadolinium-enhanced mri</t>
+  </si>
+  <si>
+    <t>cryogenically-enhanced mri</t>
+  </si>
+  <si>
+    <t>cryogenically-enhanced mri; cryogenically enhanced mri; cryogenically-cooled mri; cryo-cooled mri; cryogenic mri; cryogenically cooled magnet mri</t>
+  </si>
+  <si>
+    <t>diffusion mri</t>
+  </si>
+  <si>
+    <t>dynamic contrast-enhanced (dce) mri</t>
+  </si>
+  <si>
+    <t>dynamic contrast-enhanced mri; dce-mri; dynamic ce-mri; dce mri; dynamic contrast mri; contrast kinetic mri</t>
+  </si>
+  <si>
+    <t>fluorescence lifetime imaging microscopy (flim)</t>
+  </si>
+  <si>
+    <t>fluorescence lifetime imaging microscopy; flim; fluorescence lifetime imaging; fluorescence lifetime microscopy; time-resolved fluorescence imaging; lifetime flim</t>
+  </si>
+  <si>
+    <t>fluorescence resonance energy transfer (fret) imaging</t>
+  </si>
+  <si>
+    <t>fluorescence resonance energy transfer imaging; fret imaging; fret microscopy; förster resonance energy transfer imaging; fluorescence energy transfer imaging; fret</t>
+  </si>
+  <si>
+    <t>functional mri</t>
+  </si>
+  <si>
+    <t>functional mri; fmri; functional magnetic resonance imaging; mri functional imaging; functional mr imaging</t>
+  </si>
+  <si>
+    <t>functional pet</t>
+  </si>
+  <si>
+    <t>functional pet; fpet; functional positron emission tomography; pet functional imaging; pet physiological imaging</t>
+  </si>
+  <si>
+    <t>gated ct acquisition</t>
+  </si>
+  <si>
+    <t>gated ct acquisition; ecg-gated ct; gated ct; cardiac-gated ct; respiratory-gated ct; gated helical ct; gated acquisition ct</t>
+  </si>
+  <si>
+    <t>gray-matter shrinkage</t>
+  </si>
+  <si>
+    <t>gray-matter shrinkage; gray matter atrophy; cortical thinning; cortical atrophy; gray matter volume loss; gray-matter reduction; grey-matter shrinkage</t>
+  </si>
+  <si>
+    <t>bioluminescence imaging; bli imaging; in vivo bioluminescence imaging; bioluminescent imaging; luciferase imaging; optical bioluminescence imaging</t>
+  </si>
+  <si>
+    <t>diffusion mri; diffusion-weighted imaging; diffusion-weighted mri; diffusion tensor imaging; diffusion mr imaging; diffusion-weighted mr</t>
+  </si>
+  <si>
+    <t>perfusion mri (cbf-weighted)</t>
+  </si>
+  <si>
+    <t>perfusion mri (cbf-weighted); cbf-weighted perfusion mri; perfusion-weighted mri (cbf); cerebral blood flow mri; asl cbf imaging; arterial spin labeling (asl) mri; dsc cbf-mri; perfusion fmri (cbf); cbf imaging</t>
+  </si>
+  <si>
+    <t>perfusion mri (cbv-weighted)</t>
+  </si>
+  <si>
+    <t>perfusion mri (cbv-weighted); cbv-weighted perfusion mri; perfusion-weighted mri (cbv); cerebral blood volume mri; dsc cbv imaging; cbv fmri; dynamic susceptibility contrast (dsc) mri; perfusion fmri (cbv); cbv imaging</t>
+  </si>
+  <si>
+    <t>pharmacological mri (phmri) (amphetamine/apomorphine challenge)</t>
+  </si>
+  <si>
+    <t>pharmacological mri; phmri; drug-challenge mri; pharmaco-mri; amphetamine challenge mri; apomorphine challenge mri; phmri amphetamine; phmri apomorphine; pharmacological fmri; pharmaco-fmri; ph-fmri</t>
+  </si>
+  <si>
+    <t>photoacoustic microscopy (pam)</t>
+  </si>
+  <si>
+    <t>photoacoustic microscopy; pam; photo-acoustic microscopy; optoacoustic microscopy; optical-resolution pam; acoustic-resolution pam; micro-pam; high-resolution pam; label-free pam imaging</t>
+  </si>
+  <si>
+    <t>photoacoustic tomography</t>
+  </si>
+  <si>
+    <t>photoacoustic tomography; pat; photo-acoustic tomography; optoacoustic tomography; pact; photoacoustic ct; optoacoustic ct; volumetric pat; 3d pat; deep-tissue pat; label-free pat; reflection-mode pat</t>
+  </si>
+  <si>
+    <t>resting-state fmri</t>
+  </si>
+  <si>
+    <t>resting-state fmri; rs-fmri; resting state mri; functional connectivity mri; resting-state functional mri; resting-state bold; rs-bold; fcmri; intrinsic-activity mri</t>
+  </si>
+  <si>
+    <t>spect</t>
+  </si>
+  <si>
+    <t>spect; single-photon emission computed tomography; spect imaging; spet; gamma-camera tomography; single photon ct</t>
+  </si>
+  <si>
+    <t>structural mri</t>
+  </si>
+  <si>
+    <t>structural mri; anatomical mri; amri; structural mr imaging; t1/t2-weighted mri; high-resolution mri; morphometric mri; anatomical mr imaging</t>
+  </si>
+  <si>
+    <t>t1-weighted mri</t>
+  </si>
+  <si>
+    <t>t1-weighted mri; t1-weighted mr imaging; t1w mri; t1wi; spin-lattice–weighted mri; inversion-recovery t1; 3d t1 sequence; mprage; ir-t1</t>
+  </si>
+  <si>
+    <t>t2-weighted mri</t>
+  </si>
+  <si>
+    <t>t2-weighted mri; t2-weighted mr imaging; t2w mri; t2wi; spin-spin–weighted mri; turbo spin-echo t2; fast-spin echo t2; flair-weighted; ir-t2</t>
+  </si>
+  <si>
+    <t>targeted contrast mri</t>
+  </si>
+  <si>
+    <t>targeted contrast mri; molecular mri; ligand-targeted mri; targeted-contrast enhanced mri; contrast agent–targeted mri; receptor-targeted mri; nanoparticle-mri</t>
+  </si>
+  <si>
+    <t>two-photon imaging</t>
+  </si>
+  <si>
+    <t>two-photon imaging; 2-photon microscopy; 2pm; two-photon microscopy; multiphoton imaging; two-photon excitation microscopy; nonlinear fluorescence imaging</t>
+  </si>
+  <si>
+    <t>ultra-high-field mri</t>
+  </si>
+  <si>
+    <t>ultra-high-field mri; uhf mri; 7t mri; 9.4t mri; high-field mri; ultra-high-resolution mri; ≥7 tesla mri; uhf-mr imaging</t>
+  </si>
+  <si>
+    <t>ultrafast fmri (sms-epi)</t>
+  </si>
+  <si>
+    <t>ultrafast fmri; sms-epi fmri; multiband epi; simultaneous multi-slice fmri; rapid fmri; high-temporal fmri; sms epi; multiband echo-planar imaging</t>
+  </si>
+  <si>
+    <t>ventricular enlargement</t>
+  </si>
+  <si>
+    <t>ventricular enlargement; ventricular dilation; ventriculomegaly; lateral-ventricle enlargement; hydrocephalic dilation; enlarged ventricles; ventricle volume increase</t>
+  </si>
+  <si>
+    <t>white-matter shrinkage</t>
+  </si>
+  <si>
+    <t>white-matter shrinkage; white matter atrophy; wm volume loss; wm atrophy; white matter thinning; white-matter reduction</t>
+  </si>
+  <si>
+    <t>zte-cbv fmri</t>
+  </si>
+  <si>
+    <t>zte-cbv fmri; zero-te cbv imaging; zte cerebral blood volume fmri; zte-based cbv mri; zero-te cbv mapping; zte cbv-weighted fmri</t>
+  </si>
+  <si>
+    <t>metatranscriptomics</t>
+  </si>
+  <si>
+    <t>metatranscriptomics; meta-transcriptomics; meta transcriptomics; metatranscriptome sequencing; meta-rna-seq; environmental transcriptomics; community transcriptomics; metatranscriptome profiling</t>
+  </si>
+  <si>
+    <t>metexplore</t>
+  </si>
+  <si>
+    <t>metexplore; metexplore web; metexplore database; metexplore platform; metexplore web interface; metexplore pathway analysis platform; metexplore 2.0</t>
+  </si>
+  <si>
+    <t>mibiomics</t>
+  </si>
+  <si>
+    <t>mibiomics; microbiome omics; microbe biomics; microbial biomics; mibiomic profiling; microbial multiomics; microbiome systems biology</t>
+  </si>
+  <si>
+    <t>micro-endoscopic calcium imaging (e.g. ninscope)</t>
+  </si>
+  <si>
+    <t>micro-endoscopic calcium imaging; microendoscopic calcium imaging; micro endoscopic calcium imaging; ninscope imaging; in vivo microendoscopic calcium imaging; miniature microscope calcium imaging; one-photon microendoscopic imaging</t>
+  </si>
+  <si>
+    <t>micro-pet</t>
+  </si>
+  <si>
+    <t>micro-pet; micro pet; micropet; small-animal pet; small animal pet; µpet; preclinical pet; micro-pet imaging; micro pet imaging</t>
+  </si>
+  <si>
+    <t>microarray expression profiling</t>
+  </si>
+  <si>
+    <t>microarray expression profiling; microarray gene expression profiling; gene expression microarray; expression microarray; transcriptome microarray; gex microarray; affymetrix microarray profiling</t>
+  </si>
+  <si>
+    <t>microdialysis</t>
+  </si>
+  <si>
+    <t>microdialysis; in vivo microdialysis; intracerebral microdialysis; brain microdialysis; microdialysis sampling; microdialysis perfusion</t>
+  </si>
+  <si>
+    <t>microfluidic droplet encapsulation</t>
+  </si>
+  <si>
+    <t>microfluidic droplet encapsulation; droplet microfluidics; microdroplet encapsulation; droplet encapsulation microfluidics; microfluidic droplet generation; microfluidic droplet platform</t>
+  </si>
+  <si>
+    <t>mirna microarray / nanostring</t>
+  </si>
+  <si>
+    <t>mirna microarray; microrna microarray; mirna nanostring; nanostring mirna assay; nanostring ncounter mirna; mirna expression profiling nanostring; microRNA nCounter</t>
+  </si>
+  <si>
+    <t>molecular fmri</t>
+  </si>
+  <si>
+    <t>molecular fmri; molecular fMRI; molecular mri; molecular functional mri; molecular imaging fmri; targeted molecular fmri; functional molecular imaging</t>
+  </si>
+  <si>
+    <t>FC test; conditioned fear assay; cued FC; contextual FC</t>
+  </si>
+  <si>
+    <t>RNA-sequencing; RNA-seq; RNA sequencing; RNA seq; RNAseq; transcriptome sequencing; mRNA-seq; whole-transcriptome sequencing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">single-cell rna-seq	</t>
+  </si>
+  <si>
+    <t>single-cell rna-seq; single cell rna-seq; single-cell rna seq; single cell rna seq; single-cell rna-sequencing; single cell rna-sequencing; single-cell rna sequencing; single cell rna sequencing; sc-rna-seq; scrna-seq; sc rna-seq; sc rnaseq; scrnaseq; single-cell transcriptome sequencing; single cell transcriptome sequencing; single-cell transcriptomics; single cell transcriptomics; droplet-based scRNA-seq; plate-based scRNA-seq; microfluidic scRNA-seq; SMART-seq; 10x Genomics scRNA-seq</t>
+  </si>
+  <si>
+    <t>tail paralysis</t>
+  </si>
+  <si>
+    <t>tail paralysis; paralysis of the tail; tail drop; tail limp; tail flaccidity; lack of tail movement; immobile tail; tail motor deficit</t>
+  </si>
+  <si>
+    <t>hindlimb paresis</t>
+  </si>
+  <si>
+    <t>hindlimb paresis; hind limb paresis; hind-limb paresis; hindlimb weakness; hind leg weakness; weakness in hind legs; weakness in hind limbs; difficulty using hind legs; partial hindlimb paralysis; posterior limb paresis</t>
+  </si>
+  <si>
+    <t>bilateral hindlimb paralysis</t>
+  </si>
+  <si>
+    <t>bilateral hindlimb paralysis; paralysis of both hind legs; both hind leg paralysis; complete hindlimb paralysis; inability to move hind legs; hind limb plegia (bilateral); bilateral posterior paralysis</t>
+  </si>
+  <si>
+    <t>forelimb paralysis</t>
+  </si>
+  <si>
+    <t>forelimb paralysis; paralysis of the forelegs; front limb paralysis; inability to move forelegs; forelimb motor deficit; foreleg plegia; anterior limb paralysis</t>
+  </si>
+  <si>
+    <t>moribund status</t>
+  </si>
+  <si>
+    <t>moribund status; moribund state; moribund condition; near-death state; terminal condition; pre-moribund state; animal moribund; critical condition</t>
+  </si>
+  <si>
+    <t>clinical score evaluation</t>
+  </si>
+  <si>
+    <t>clinical score evaluation; clinical scoring; clinical assessment score; symptom scoring; severity scoring; functional scoring; neurological score; disease severity score; scoring of clinical signs</t>
+  </si>
+  <si>
+    <t>electroencephalography; EEG recording; electrical brain activity recording; EEG-video</t>
+  </si>
+  <si>
+    <t>electroencephalography; eeg; electroencephalogram; eeg recording; eeg monitoring; encephalography; electroencephalograph</t>
+  </si>
+  <si>
+    <t>electrocardiography (ecg)</t>
+  </si>
+  <si>
+    <t>electrocardiography; ecg; ekg; electrocardiogram; ecg recording; ecg monitoring; cardiogram</t>
+  </si>
+  <si>
+    <t>electroretinography (erg)</t>
+  </si>
+  <si>
+    <t>electroretinography; erg; electroretinogram; erg recording; flash erg; pattern erg; multifocal erg (mferg); photopic erg; scotopic erg; electroretinographic test</t>
+  </si>
+  <si>
+    <t>electroneurography (enog)</t>
+  </si>
+  <si>
+    <t>electroneurography; enog; electroneurogram; enog test; electroneurographic study; nerve conduction study</t>
+  </si>
+  <si>
+    <t>electromyography (emg)</t>
+  </si>
+  <si>
+    <t>electromyography; emg; electromyogram; emg recording; needle emg; surface emg; motor-unit potential recording</t>
+  </si>
+  <si>
+    <t>sensory-evoked potentials (eps)</t>
+  </si>
+  <si>
+    <t>sensory-evoked potentials; seps; sensory evoked potentials; evoked potentials; somatosensory evoked potentials; sensory eps; ep recording</t>
+  </si>
+  <si>
+    <t>multiunit extracellular recording</t>
+  </si>
+  <si>
+    <t>multiunit extracellular recording; multi-unit extracellular recording; extracellular multiunit recording; multiunit action-potential recording; mua recording; extracellular mua; multiunit spike recording</t>
+  </si>
+  <si>
+    <t>single-unit extracellular recording</t>
+  </si>
+  <si>
+    <t>single-unit extracellular recording; single unit extracellular recording; extracellular single-unit recording; single-unit spike recording; sua recording; extracellular sua; single neuron recording</t>
+  </si>
+  <si>
+    <t>microneurography</t>
+  </si>
+  <si>
+    <t>microneurography; micro-neurography; percutaneous microneurography; microneurographic recording; nerve-fiber recording; cutaneous nerve recording</t>
+  </si>
+  <si>
+    <t>teased-fiber single-unit recording</t>
+  </si>
+  <si>
+    <t>teased-fiber single-unit recording; teased fiber single unit recording; fiber-teased single-unit recording; teased-fiber extracellular recording</t>
+  </si>
+  <si>
+    <t>hippocampal slice field potential</t>
+  </si>
+  <si>
+    <t>hippocampal slice field potential; hippocampal slice field-potential recording; slice field potential recording; hippocampal fpr; field-potential recording in hippocampal slice</t>
+  </si>
+  <si>
+    <t>brain slice multiunit recording</t>
+  </si>
+  <si>
+    <t>brain slice multiunit recording; brain-slice multi-unit recording; slice multiunit extracellular recording; brain slice mua recording; slice mua</t>
+  </si>
+  <si>
+    <t>clinical electrophysiology evaluation</t>
+  </si>
+  <si>
+    <t>clinical electrophysiology evaluation; clinical electrophysiological evaluation; clinical neurophysiology evaluation; electrophysiological assessment; clinical neurophysiology assessment</t>
+  </si>
+  <si>
+    <t>hippocampal slice fepsp recording</t>
+  </si>
+  <si>
+    <t>hippocampal slice fepsp recording; hippocampal slice f-epsp recording; hippocampal fepsp recording; slice fepsp recording (hippocampal); field excitatory postsynaptic potential recording in hippocampal slice; excitatory postsynaptic potential fepsp assay</t>
+  </si>
+  <si>
+    <t>cortical slice field potential</t>
+  </si>
+  <si>
+    <t>cortical slice field potential; cortical slice field-potential recording; cortical fpr recording; slice field potential recording (cortical); field potential recording in cortical slice; cortical slice fpr assay</t>
+  </si>
+  <si>
+    <t>cerebellar slice field potential</t>
+  </si>
+  <si>
+    <t>cerebellar slice field potential; cerebellar slice field-potential recording; cerebellar fpr recording; slice field potential recording (cerebellar); field potential recording in cerebellar slice; cerebellar slice fpr assay</t>
+  </si>
+  <si>
+    <t>brain slice multiunit spike recording</t>
+  </si>
+  <si>
+    <t>brain slice multiunit spike recording; brain-slice multiunit spike recording; brain slice mua spike recording; slice multiunit spike recording (brain); brain slice multiunit extracellular spike recording; brain slice mua assay</t>
+  </si>
+  <si>
+    <t>multielectrode array (mea) recording</t>
+  </si>
+  <si>
+    <t>multielectrode array recording; mea recording; mea electrophysiology; mea extracellular recording; mea spike recording; multielectrode array electrophysiology; multielectrode array spike recording; mea network activity recording</t>
+  </si>
+  <si>
+    <t>optogenetically-evoked extracellular recording</t>
+  </si>
+  <si>
+    <t>optogenetically-evoked extracellular recording; optogenetic extracellular recording; optogenetic-evoked mua recording; light-evoked extracellular spike recording; photostimulation extracellular recording; opto-mua recording</t>
+  </si>
+  <si>
+    <t>ussing chamber transepithelial current clamp</t>
+  </si>
+  <si>
+    <t>ussing chamber transepithelial current clamp; ussing chamber current clamp; transepithelial current clamp; epithelial current clamp assay; transepithelial electrophysiology; ussing chamber ion transport measurement</t>
+  </si>
+  <si>
+    <t>cellular impedance assay</t>
+  </si>
+  <si>
+    <t>cellular impedance assay; cell impedance assay; electrical impedance spectroscopy; eis assay; cell-based impedance measurement; cellular dielectric spectroscopy; impedance-based cell assay; biosensor impedance assay</t>
+  </si>
+  <si>
+    <t>sharp microelectrode intracellular recording</t>
+  </si>
+  <si>
+    <t>sharp microelectrode intracellular recording; sharp-electrode intracellular recording; intracellular sharp-electrode recording; sharp microelectrode recording; intracellular microelectrode recording; sharp micropipette recording; sharp electrode impalement recording</t>
+  </si>
+  <si>
+    <t>cell-attached patch-clamp</t>
+  </si>
+  <si>
+    <t>cell-attached patch-clamp; cell attached patch clamp; cell-attached patch clamp; cell-attached pipette recording; cell-attached configuration; patch clamp (cell-attached); cell-attached patch recording; cell-attached mode recording</t>
+  </si>
+  <si>
+    <t>whole-cell patch-clamp</t>
+  </si>
+  <si>
+    <t>whole-cell patch-clamp; whole cell patch clamp; whole-cell patch clamp; whole cell patch-clamp; whole-cell pipette recording; whole-cell configuration; patch clamp (whole-cell); whole-cell patch recording; ruptured-patch recording</t>
+  </si>
+  <si>
+    <t>inside-out patch-clamp</t>
+  </si>
+  <si>
+    <t>inside-out patch-clamp; inside out patch clamp; inside-out patch clamp; inside out patch-clamp; inside-out configuration; inside-out patch recording; excised inside-out patch; inside-out pipette recording</t>
+  </si>
+  <si>
+    <t>outside-out patch-clamp</t>
+  </si>
+  <si>
+    <t>outside-out patch-clamp; outside out patch clamp; outside-out patch clamp; outside out patch-clamp; outside-out configuration; outside-out patch recording; excised outside-out patch; outside-out pipette recording</t>
+  </si>
+  <si>
+    <t>artificial lipid bilayer recording</t>
+  </si>
+  <si>
+    <t>artificial lipid bilayer recording; artificial lipid-bilayer recording; planar lipid bilayer recording; planar lipid-bilayer recording; black lipid membrane recording; blm recording; bilayer electrophysiology; bilayer single-channel recording; artificial membrane recording; reconstituted lipid bilayer recording; lipid bilayer assay</t>
+  </si>
+  <si>
+    <t>current-clamp recording</t>
+  </si>
+  <si>
+    <t>current-clamp recording; current clamp recording; current-clamp electrophysiology; current clamp mode; current-injection recording; bridge-mode recording; intracellular current clamp; whole-cell current-clamp; sharp-electrode current clamp; current clamp patch-clamp</t>
+  </si>
+  <si>
+    <t>voltage-clamp recording</t>
+  </si>
+  <si>
+    <t>voltage-clamp recording; voltage clamp recording; voltage-clamp electrophysiology; voltage clamp mode; voltage-control recording; two-electrode voltage clamp; tevc; patch-clamp voltage-clamp; whole-cell voltage-clamp; membrane potential clamp; voltage clamp assay</t>
+  </si>
+  <si>
+    <t>western blot; western-blot; western blotting; western-blotting; immunoblot; immunoblotting; western immunoblot; western immunoblotting; protein blot; sds-page immunoblot; wb; wb assay; western blot analysis; protein immunoblot assay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hindlimb paralysis	</t>
+  </si>
+  <si>
+    <t>hindlimb paralysis; hind limb paralysis; hind-leg paralysis; paralysis of hindlimbs; posterior limb paralysis; hindleg paralysis; complete hindlimb paralysis; hindlimb plegia; inability to use hind legs; hindlimb motor deficit</t>
   </si>
 </sst>
 </file>
@@ -2722,10 +3556,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F7C088-4AE2-FE43-98E3-B1584DF0C0CC}">
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="1" max="1" width="62.6640625" customWidth="1"/>
     <col min="2" max="2" width="82.1640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2755,82 +3589,82 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -3278,2583 +4112,3703 @@
         <v>116</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>981</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>117</v>
+      </c>
+      <c r="B70" t="s">
         <v>118</v>
-      </c>
-      <c r="B70" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" t="s">
         <v>120</v>
-      </c>
-      <c r="B71" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>121</v>
+      </c>
+      <c r="B72" t="s">
         <v>122</v>
-      </c>
-      <c r="B72" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" t="s">
         <v>124</v>
-      </c>
-      <c r="B73" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>125</v>
+      </c>
+      <c r="B74" t="s">
         <v>126</v>
-      </c>
-      <c r="B74" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" t="s">
         <v>128</v>
-      </c>
-      <c r="B75" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>129</v>
+      </c>
+      <c r="B76" t="s">
         <v>130</v>
-      </c>
-      <c r="B76" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77" t="s">
         <v>132</v>
-      </c>
-      <c r="B77" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>133</v>
+      </c>
+      <c r="B78" t="s">
         <v>134</v>
-      </c>
-      <c r="B78" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>135</v>
+      </c>
+      <c r="B79" t="s">
         <v>136</v>
-      </c>
-      <c r="B79" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B80" t="s">
-        <v>139</v>
+        <v>965</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B81" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B82" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B83" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B86" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B87" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B88" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B90" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B91" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B92" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B93" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B95" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B97" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B98" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B99" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B100" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B101" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B102" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B103" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B104" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B105" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B106" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B107" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B108" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B109" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B110" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B111" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B112" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B113" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B114" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B115" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B116" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B117" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B118" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B119" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B120" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B121" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B122" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B123" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B124" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B125" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B126" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B127" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B128" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B129" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B130" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B131" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B132" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B133" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B134" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B135" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B136" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B137" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B138" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B139" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B140" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B142" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B143" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B144" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B145" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B146" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B147" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B148" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B149" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B150" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B151" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B152" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B153" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B154" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B155" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B156" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B157" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B158" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B159" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B160" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B161" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B162" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B163" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B164" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B165" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>310</v>
-      </c>
-      <c r="B166" t="s">
-        <v>311</v>
+        <v>308</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>312</v>
-      </c>
-      <c r="B167" t="s">
-        <v>313</v>
+        <v>309</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>315</v>
+        <v>498</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>316</v>
+        <v>499</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>510</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>498</v>
+        <v>311</v>
+      </c>
+      <c r="B177" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>511</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>499</v>
+        <v>313</v>
+      </c>
+      <c r="B178" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B179" t="s">
-        <v>318</v>
+        <v>495</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B180" t="s">
-        <v>500</v>
+        <v>316</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B181" t="s">
-        <v>501</v>
+        <v>318</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B182" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B183" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B184" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B185" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B186" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B187" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B188" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B190" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B191" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B192" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B193" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B194" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B195" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B196" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B197" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B198" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B199" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B200" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B201" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B202" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B203" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B204" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B205" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B206" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B207" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B208" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B209" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B210" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B211" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B212" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B213" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B214" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B215" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B216" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B217" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B218" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B219" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B220" t="s">
-        <v>398</v>
+        <v>496</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B221" t="s">
-        <v>400</v>
+        <v>497</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B222" t="s">
-        <v>502</v>
+        <v>398</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B223" t="s">
-        <v>503</v>
+        <v>400</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B224" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B225" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B226" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B227" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B228" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B229" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B230" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B231" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B232" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B233" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B234" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B235" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B236" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B237" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B238" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B239" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B240" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B241" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B242" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B243" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B244" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B245" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B246" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B247" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B248" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B249" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B250" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B251" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B252" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B253" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B254" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>465</v>
-      </c>
-      <c r="B255" t="s">
-        <v>466</v>
+        <v>506</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>467</v>
-      </c>
-      <c r="B256" t="s">
-        <v>468</v>
+        <v>508</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>661</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
+        <v>661</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B343" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B342" s="3" t="s">
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344" s="3" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A343" t="s">
+      <c r="B344" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="B343" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A344" t="s">
-        <v>668</v>
-      </c>
-      <c r="B344" s="3" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" s="3" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" s="3" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" s="3" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" s="3" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
         <v>685</v>
       </c>
-      <c r="B353" s="3" t="s">
+      <c r="B354" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A354" s="3" t="s">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
         <v>687</v>
       </c>
-      <c r="B354" s="3" t="s">
+      <c r="B355" t="s">
         <v>688</v>
-      </c>
-    </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A355" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="B355" s="3" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B356" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B357" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B358" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B359" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B360" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B361" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B362" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B363" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B364" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B365" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B366" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B367" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B368" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B369" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B370" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B371" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B372" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B373" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B374" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B375" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B376" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B377" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B378" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B379" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B380" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B381" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B382" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B383" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B384" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B385" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B386" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B387" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B388" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
+        <v>755</v>
+      </c>
+      <c r="B389" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B390" t="s">
         <v>758</v>
       </c>
-      <c r="B389" t="s">
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391" s="2" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A390" t="s">
+      <c r="B391" t="s">
         <v>760</v>
       </c>
-      <c r="B390" t="s">
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392" s="2" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A391" t="s">
+      <c r="B392" t="s">
         <v>762</v>
       </c>
-      <c r="B391" t="s">
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393" s="2" t="s">
         <v>763</v>
+      </c>
+      <c r="B393" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B394" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B395" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A396" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B396" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A397" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B397" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A398" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B398" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A399" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B399" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A400" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B400" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A401" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B401" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A402" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B402" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B403" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A404" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B404" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A405" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B405" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A406" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B406" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A407" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B407" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A408" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B408" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A409" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B409" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A410" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B410" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A411" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B411" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A412" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B412" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A413" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B413" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A414" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B414" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A415" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B415" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A416" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B416" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A417" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B417" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A418" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B418" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A419" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B419" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A420" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="B420" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A421" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B421" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A422" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B422" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A423" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B423" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A424" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B424" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A425" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B425" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A426" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B426" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A427" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B427" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A428" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B428" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A429" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B429" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A430" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B430" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A431" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B431" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A432" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B432" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A433" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B433" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A434" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B434" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A435" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B435" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A436" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B436" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A437" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B437" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A438" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B438" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A439" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B439" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A440" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B440" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A441" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B441" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A442" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B442" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A443" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B443" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A444" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B444" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A445" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B445" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A446" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B446" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A447" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B447" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A448" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B448" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A449" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B449" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A450" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B450" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A451" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B451" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A452" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B452" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A453" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B453" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A454" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B454" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A455" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="B455" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A456" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B456" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A457" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B457" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A458" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="B458" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A459" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B459" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A460" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B460" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A461" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B461" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A462" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="B462" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A463" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="B463" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A464" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B464" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A465" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="B465" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A466" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="B466" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A467" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B467" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A468" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B468" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A469" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="B469" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A470" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="B470" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A471" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B471" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A472" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B472" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A473" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B473" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A474" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B474" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A475" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="B475" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A476" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="B476" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A477" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B477" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A478" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B478" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A479" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B479" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A480" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B480" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A481" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B481" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A482" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B482" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A483" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B483" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A484" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B484" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A485" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="B485" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A486" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B486" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A487" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B487" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A488" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B488" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A489" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B489" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A490" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B490" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A491" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B491" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A492" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B492" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A493" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="B493" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A494" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="B494" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A495" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B495" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A496" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B496" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A497" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A498" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B498" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A499" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B499" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A500" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B500" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A501" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B501" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A502" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="B502" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A503" t="s">
+        <v>116</v>
+      </c>
+      <c r="B503" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A504" t="s">
+        <v>983</v>
+      </c>
+      <c r="B504" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A505" t="s">
+        <v>985</v>
+      </c>
+      <c r="B505" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A506" t="s">
+        <v>987</v>
+      </c>
+      <c r="B506" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A507" t="s">
+        <v>989</v>
+      </c>
+      <c r="B507" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A508" t="s">
+        <v>991</v>
+      </c>
+      <c r="B508" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A509" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B509" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A510" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="B510" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A511" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B511" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A512" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A513" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A514" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A515" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A516" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A517" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A518" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A519" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A520" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A521" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A522" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A523" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A524" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A525" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A526" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A527" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A528" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A529" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A530" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A531" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1038</v>
       </c>
     </row>
   </sheetData>

--- a/03_IE_tasks/data/related/outcomes_endpoints/harmonized_synonyms_GPT.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/harmonized_synonyms_GPT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F6706C-74F0-FA4C-BF90-5C7D8F752AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABB20B0-155F-CC41-ABE8-E59FA75B4B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51000" yWindow="7740" windowWidth="30240" windowHeight="17740" xr2:uid="{15501CB9-9377-134A-A4EA-E637D4B0B337}"/>
+    <workbookView xWindow="37640" yWindow="7400" windowWidth="42000" windowHeight="17740" xr2:uid="{15501CB9-9377-134A-A4EA-E637D4B0B337}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1068">
   <si>
     <t>Canonical Name</t>
   </si>
@@ -2036,9 +2036,6 @@
     <t>body weight measurement</t>
   </si>
   <si>
-    <t>body weight check; body weight measurement; body weight monitoring; weighing procedure; weighing record; weighing session; weight tracking</t>
-  </si>
-  <si>
     <t>circular locomotion test</t>
   </si>
   <si>
@@ -2336,9 +2333,6 @@
     <t>qrt-pcr array</t>
   </si>
   <si>
-    <t>qRT-PCR array; qRT PCR array; quantitative real-time PCR array; qPCR array; realtime PCR array; qRT-PCR panel; quantitative RT-PCR array</t>
-  </si>
-  <si>
     <t>recon3d</t>
   </si>
   <si>
@@ -2948,15 +2942,9 @@
     <t>tail paralysis</t>
   </si>
   <si>
-    <t>tail paralysis; paralysis of the tail; tail drop; tail limp; tail flaccidity; lack of tail movement; immobile tail; tail motor deficit</t>
-  </si>
-  <si>
     <t>hindlimb paresis</t>
   </si>
   <si>
-    <t>hindlimb paresis; hind limb paresis; hind-limb paresis; hindlimb weakness; hind leg weakness; weakness in hind legs; weakness in hind limbs; difficulty using hind legs; partial hindlimb paralysis; posterior limb paresis</t>
-  </si>
-  <si>
     <t>bilateral hindlimb paralysis</t>
   </si>
   <si>
@@ -2972,15 +2960,9 @@
     <t>moribund status</t>
   </si>
   <si>
-    <t>moribund status; moribund state; moribund condition; near-death state; terminal condition; pre-moribund state; animal moribund; critical condition</t>
-  </si>
-  <si>
     <t>clinical score evaluation</t>
   </si>
   <si>
-    <t>clinical score evaluation; clinical scoring; clinical assessment score; symptom scoring; severity scoring; functional scoring; neurological score; disease severity score; scoring of clinical signs</t>
-  </si>
-  <si>
     <t>electroencephalography; EEG recording; electrical brain activity recording; EEG-video</t>
   </si>
   <si>
@@ -3161,7 +3143,103 @@
     <t xml:space="preserve">hindlimb paralysis	</t>
   </si>
   <si>
-    <t>hindlimb paralysis; hind limb paralysis; hind-leg paralysis; paralysis of hindlimbs; posterior limb paralysis; hindleg paralysis; complete hindlimb paralysis; hindlimb plegia; inability to use hind legs; hindlimb motor deficit</t>
+    <t>tail paralysis; paralysis of the tail; tail drop; tail limp; tail flaccidity; lack of tail movement; immobile tail; tail motor deficit; limp tail</t>
+  </si>
+  <si>
+    <t>moribund status; moribund; moribund state; moribund condition; near-death state; terminal condition; pre-moribund state; animal moribund; critical condition</t>
+  </si>
+  <si>
+    <t>body weight check; body weight measurement; body weight monitoring; weighing procedure; weighing record; weighing session; weight tracking; weight loss</t>
+  </si>
+  <si>
+    <t>qRT-PCR array; real-time PCR; real time PCR; qRT PCR array; quantitative real-time PCR array; qPCR array; realtime PCR array; qRT-PCR panel; quantitative RT-PCR array</t>
+  </si>
+  <si>
+    <t>swiss-pdbviewer</t>
+  </si>
+  <si>
+    <t>swiss-pdbviewer; swiss pdb viewer; swiss-pdb viewer; swiss-pdb-viewer; swiss pdb-viewer; spdbv; spdb; deepview; deep view; deep-view; swiss-pdbviewer software; swiss pdbviewer tool; expasy swiss-pdbviewer; pdbviewer</t>
+  </si>
+  <si>
+    <t>x-ray crystallography</t>
+  </si>
+  <si>
+    <t>x-ray crystallography; x ray crystallography; xray crystallography; protein x-ray crystallography; macromolecular x-ray crystallography; x-ray diffraction; xrd; crystallographic analysis</t>
+  </si>
+  <si>
+    <t>nmr spectroscopy</t>
+  </si>
+  <si>
+    <t>nmr spectroscopy; nmr; nuclear magnetic resonance spectroscopy; nuclear magnetic resonance; nmrs; nmr spectrometry; nmr analysis; proton nmr; heteronuclear nmr</t>
+  </si>
+  <si>
+    <t>cryo-electron microscopy</t>
+  </si>
+  <si>
+    <t>cryo-electron microscopy; cryoelectron microscopy; cryo-em; cryo em; cryogenic electron microscopy; cryo-tem; cryo-tem imaging; cryo-transmission electron microscopy</t>
+  </si>
+  <si>
+    <t>electron tomography</t>
+  </si>
+  <si>
+    <t>electron tomography; et; electron-tomography; tomographic electron microscopy; electron tomographic imaging; 3d electron tomography</t>
+  </si>
+  <si>
+    <t>3d modeling</t>
+  </si>
+  <si>
+    <t>3d modeling; three-dimensional modeling; three dimensional modeling; 3d structure modeling; 3d structural modeling; model building; three-dimensional reconstruction; 3d reconstruction</t>
+  </si>
+  <si>
+    <t>ccp4</t>
+  </si>
+  <si>
+    <t>ccp4; ccp-4; collaborative computational project 4; ccp4 suite; ccp4 software; ccp4 package; ccp4 program; ccp4 toolkit</t>
+  </si>
+  <si>
+    <t>modeller</t>
+  </si>
+  <si>
+    <t>modeller; modeller software; modeller program; modeller comparative modeling; modeller homology modeling; automodel (modeller); modeller pipeline; modeller structure prediction</t>
+  </si>
+  <si>
+    <t>alphafold</t>
+  </si>
+  <si>
+    <t>alphafold; alpha fold; deepmind alphafold; alphafold2; alphafold protein structure prediction; alphafold modeling; alphafold database entries; alphafold predictions</t>
+  </si>
+  <si>
+    <t>hindlimb paralysis; hind limb paralysis; hind-leg paralysis; paralysis of hindlimbs; paralysis of hind limbs; posterior limb paralysis; hindleg paralysis; complete hindlimb paralysis; hindlimb plegia; inability to use hind legs; hindlimb motor deficit;</t>
+  </si>
+  <si>
+    <t>3d image analysis</t>
+  </si>
+  <si>
+    <t>3d image analysis; three-dimensional image analysis; 3d imaging analysis; volumetric image analysis; 3d volumetric analysis; three dimensional imaging analysis; 3d image processing; 3d quantitative image analysis; volumetric microscopy analysis; 3d reconstruction and analysis; 3d morphological analysis; multi-view 3d image analysis; 3d segmentation and analysis; confocal 3d image analysis; 3d image quantification; 3d rendering analysis</t>
+  </si>
+  <si>
+    <t>clinical score evaluation; clinical signs; clinical scoring; clinical assessment score; symptom scoring; severity scoring; functional scoring; neurological score; disease severity score; scoring of clinical signs</t>
+  </si>
+  <si>
+    <t>elisa</t>
+  </si>
+  <si>
+    <t>elisa; enzyme-linked immunosorbent assay; enzyme linked immunosorbent assay; enzyme immunoassay; eia; immunoenzymatic assay; sandwich elisa; competitive elisa; indirect elisa; direct elisa; colorimetric elisa; fluorometric elisa; chemiluminescent elisa; microplate elisa; quantitative elisa; rapid elisa; multiplex elisa; elisa assay; elisa analysis</t>
+  </si>
+  <si>
+    <t>hindlimb paresis; hind limb paresis; hind-limb paresis; hindlimb weakness; hind leg weakness; weakness in hind legs; weakness in hind limbs; weakness in hind limb; difficulty using hind legs; partial hindlimb paralysis; posterior limb paresis; hind leg weakness</t>
+  </si>
+  <si>
+    <t>tail weakness</t>
+  </si>
+  <si>
+    <t>tail weakness; weakness in tail; weak tail; tail limp; limp tail; reduced tail strength; decreased tail tone; tail hypotonia; tail flaccidity; flaccid tail; impaired tail movement; tail motor deficit; caudal weakness; caudal paresis; tail paresis; paretic tail; lack of tail support; droopy tail</t>
+  </si>
+  <si>
+    <t>forelimb paresis</t>
+  </si>
+  <si>
+    <t>forelimb paresis; fore limb paresis; fore-limb paresis; forelimb weakness; weakness in forelegs; weakness in fore limbs; fore leg weakness; foreleg paresis; anterior limb paresis; front limb paresis; partial forelimb paralysis; inability to use fore legs; forelimb motor deficit; decreased forelimb strength; forelimb hypotonia; forelimb motor impairment</t>
   </si>
 </sst>
 </file>
@@ -3556,11 +3634,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F7C088-4AE2-FE43-98E3-B1584DF0C0CC}">
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B544"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="62.6640625" customWidth="1"/>
-    <col min="2" max="2" width="82.1640625" customWidth="1"/>
+    <col min="1" max="1" width="42.83203125" customWidth="1"/>
+    <col min="2" max="2" width="117.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -4112,7 +4190,7 @@
         <v>116</v>
       </c>
       <c r="B69" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4200,7 +4278,7 @@
         <v>137</v>
       </c>
       <c r="B80" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -6280,7 +6358,7 @@
         <v>658</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
@@ -6312,575 +6390,575 @@
         <v>665</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>666</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B345" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="B345" s="3" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B346" s="3" t="s">
         <v>669</v>
-      </c>
-      <c r="B346" s="3" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B348" s="3" t="s">
         <v>672</v>
-      </c>
-      <c r="B348" s="3" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="B349" s="3" t="s">
         <v>674</v>
-      </c>
-      <c r="B349" s="3" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B350" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="B350" s="3" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="B351" s="3" t="s">
         <v>678</v>
-      </c>
-      <c r="B351" s="3" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B352" s="3" t="s">
         <v>680</v>
-      </c>
-      <c r="B352" s="3" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B353" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="B353" s="3" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
+        <v>684</v>
+      </c>
+      <c r="B354" t="s">
         <v>685</v>
-      </c>
-      <c r="B354" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
+        <v>686</v>
+      </c>
+      <c r="B355" t="s">
         <v>687</v>
-      </c>
-      <c r="B355" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
+        <v>688</v>
+      </c>
+      <c r="B356" t="s">
         <v>689</v>
-      </c>
-      <c r="B356" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
+        <v>690</v>
+      </c>
+      <c r="B357" t="s">
         <v>691</v>
-      </c>
-      <c r="B357" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
+        <v>692</v>
+      </c>
+      <c r="B358" t="s">
         <v>693</v>
-      </c>
-      <c r="B358" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
+        <v>694</v>
+      </c>
+      <c r="B359" t="s">
         <v>695</v>
-      </c>
-      <c r="B359" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
+        <v>696</v>
+      </c>
+      <c r="B360" t="s">
         <v>697</v>
-      </c>
-      <c r="B360" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
+        <v>698</v>
+      </c>
+      <c r="B361" t="s">
         <v>699</v>
-      </c>
-      <c r="B361" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
+        <v>700</v>
+      </c>
+      <c r="B362" t="s">
         <v>701</v>
-      </c>
-      <c r="B362" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
+        <v>702</v>
+      </c>
+      <c r="B363" t="s">
         <v>703</v>
-      </c>
-      <c r="B363" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
+        <v>704</v>
+      </c>
+      <c r="B364" t="s">
         <v>705</v>
-      </c>
-      <c r="B364" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
+        <v>706</v>
+      </c>
+      <c r="B365" t="s">
         <v>707</v>
-      </c>
-      <c r="B365" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
+        <v>708</v>
+      </c>
+      <c r="B366" t="s">
         <v>709</v>
-      </c>
-      <c r="B366" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
+        <v>710</v>
+      </c>
+      <c r="B367" t="s">
         <v>711</v>
-      </c>
-      <c r="B367" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
+        <v>712</v>
+      </c>
+      <c r="B368" t="s">
         <v>713</v>
-      </c>
-      <c r="B368" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
+        <v>714</v>
+      </c>
+      <c r="B369" t="s">
         <v>715</v>
-      </c>
-      <c r="B369" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
+        <v>716</v>
+      </c>
+      <c r="B370" t="s">
         <v>717</v>
-      </c>
-      <c r="B370" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
+        <v>718</v>
+      </c>
+      <c r="B371" t="s">
         <v>719</v>
-      </c>
-      <c r="B371" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
+        <v>720</v>
+      </c>
+      <c r="B372" t="s">
         <v>721</v>
-      </c>
-      <c r="B372" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
+        <v>722</v>
+      </c>
+      <c r="B373" t="s">
         <v>723</v>
-      </c>
-      <c r="B373" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
+        <v>724</v>
+      </c>
+      <c r="B374" t="s">
         <v>725</v>
-      </c>
-      <c r="B374" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
+        <v>726</v>
+      </c>
+      <c r="B375" t="s">
         <v>727</v>
-      </c>
-      <c r="B375" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
+        <v>728</v>
+      </c>
+      <c r="B376" t="s">
         <v>729</v>
-      </c>
-      <c r="B376" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
+        <v>730</v>
+      </c>
+      <c r="B377" t="s">
         <v>731</v>
-      </c>
-      <c r="B377" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
+        <v>732</v>
+      </c>
+      <c r="B378" t="s">
         <v>733</v>
-      </c>
-      <c r="B378" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
+        <v>734</v>
+      </c>
+      <c r="B379" t="s">
         <v>735</v>
-      </c>
-      <c r="B379" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
+        <v>736</v>
+      </c>
+      <c r="B380" t="s">
         <v>737</v>
-      </c>
-      <c r="B380" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
+        <v>738</v>
+      </c>
+      <c r="B381" t="s">
         <v>739</v>
-      </c>
-      <c r="B381" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
+        <v>740</v>
+      </c>
+      <c r="B382" t="s">
         <v>741</v>
-      </c>
-      <c r="B382" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
+        <v>742</v>
+      </c>
+      <c r="B383" t="s">
         <v>743</v>
-      </c>
-      <c r="B383" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
+        <v>744</v>
+      </c>
+      <c r="B384" t="s">
         <v>745</v>
-      </c>
-      <c r="B384" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
+        <v>746</v>
+      </c>
+      <c r="B385" t="s">
         <v>747</v>
-      </c>
-      <c r="B385" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
+        <v>748</v>
+      </c>
+      <c r="B386" t="s">
         <v>749</v>
-      </c>
-      <c r="B386" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
+        <v>750</v>
+      </c>
+      <c r="B387" t="s">
         <v>751</v>
-      </c>
-      <c r="B387" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
+        <v>752</v>
+      </c>
+      <c r="B388" t="s">
         <v>753</v>
-      </c>
-      <c r="B388" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
+        <v>754</v>
+      </c>
+      <c r="B389" t="s">
         <v>755</v>
-      </c>
-      <c r="B389" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A390" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B390" t="s">
         <v>757</v>
-      </c>
-      <c r="B390" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B391" t="s">
         <v>759</v>
-      </c>
-      <c r="B391" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B392" t="s">
         <v>761</v>
-      </c>
-      <c r="B392" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B393" t="s">
         <v>763</v>
-      </c>
-      <c r="B393" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A394" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B394" t="s">
-        <v>766</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A395" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B395" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A396" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B396" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B397" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B398" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B399" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A400" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B400" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B401" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A402" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B402" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A403" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B403" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A404" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B404" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B405" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B406" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A407" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B407" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B408" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A409" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B409" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A410" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B410" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B411" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B412" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A413" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B413" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A414" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B414" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A415" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B415" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
@@ -6888,695 +6966,695 @@
         <v>365</v>
       </c>
       <c r="B416" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B417" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A418" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B418" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A419" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B419" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A420" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B420" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A421" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B421" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A422" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B422" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A423" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B423" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A424" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B424" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A425" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B425" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A426" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B426" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A427" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B427" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B428" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A429" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B429" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A430" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B430" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A431" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B431" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A432" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B432" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A433" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B433" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A434" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B434" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A435" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B435" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A436" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B436" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B437" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A438" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B438" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A439" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B439" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A440" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B440" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B441" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B442" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B443" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" s="2" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B444" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B445" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A446" s="2" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B446" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A447" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B447" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B448" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B449" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B450" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A451" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B451" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B452" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B453" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A454" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B454" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A455" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B455" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A456" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B456" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A457" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B457" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A458" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B458" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B459" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B460" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B461" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A462" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B462" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A463" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B463" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A464" s="2" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B464" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A465" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B465" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A466" s="2" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B466" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A467" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B467" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A468" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B468" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B469" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A470" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B470" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A471" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B471" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A472" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B472" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A473" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B473" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A474" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B474" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B475" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A476" s="2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B476" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A477" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B477" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A478" s="2" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B478" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A479" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B479" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A480" s="2" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B480" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A481" s="2" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B481" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A482" s="2" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B482" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A483" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B483" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B484" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A485" s="2" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B485" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A486" s="2" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B486" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A487" s="2" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B487" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A488" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B488" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A489" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B489" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A490" s="2" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B490" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A491" s="2" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B491" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A492" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B492" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A493" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B493" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A494" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B494" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A495" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B495" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A496" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B496" t="s">
-        <v>970</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A497" s="2" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="B497" t="s">
-        <v>1041</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A498" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B498" t="s">
-        <v>972</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A499" s="2" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B499" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A500" s="2" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B500" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A501" s="2" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B501" t="s">
-        <v>978</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A502" s="2" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="B502" t="s">
-        <v>980</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
@@ -7584,231 +7662,335 @@
         <v>116</v>
       </c>
       <c r="B503" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B504" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="B505" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B506" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="B507" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="B508" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A509" s="2" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="B509" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" s="2" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="B510" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A511" s="2" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B511" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" s="2" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="B512" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" s="2" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="B513" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" s="2" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="B514" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" s="2" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="B515" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" s="2" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="B516" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" s="2" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="B517" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" s="2" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="B518" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" s="2" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B519" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" s="2" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B520" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" s="2" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B521" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" s="2" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="B522" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" s="2" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B523" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" s="2" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="B524" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" s="2" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B525" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" s="2" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="B526" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="B527" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" s="2" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="B528" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" s="2" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="B529" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="B530" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" s="2" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="B531" t="s">
-        <v>1038</v>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A532" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A533" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A534" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A535" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A536" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A537" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A538" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A539" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A540" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A541" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A542" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A543" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A544" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1067</v>
       </c>
     </row>
   </sheetData>

--- a/03_IE_tasks/data/related/outcomes_endpoints/harmonized_synonyms_GPT.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/harmonized_synonyms_GPT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABB20B0-155F-CC41-ABE8-E59FA75B4B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE64587-49ED-C440-81DF-8E753FC76604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37640" yWindow="7400" windowWidth="42000" windowHeight="17740" xr2:uid="{15501CB9-9377-134A-A4EA-E637D4B0B337}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{15501CB9-9377-134A-A4EA-E637D4B0B337}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="1122">
   <si>
     <t>Canonical Name</t>
   </si>
@@ -3240,6 +3240,168 @@
   </si>
   <si>
     <t>forelimb paresis; fore limb paresis; fore-limb paresis; forelimb weakness; weakness in forelegs; weakness in fore limbs; fore leg weakness; foreleg paresis; anterior limb paresis; front limb paresis; partial forelimb paralysis; inability to use fore legs; forelimb motor deficit; decreased forelimb strength; forelimb hypotonia; forelimb motor impairment</t>
+  </si>
+  <si>
+    <t>microarray analysis</t>
+  </si>
+  <si>
+    <t>microarray analysis; microarray data analysis; array analysis; gene chip data analysis; high-throughput microarray analysis; microarray-based profiling; array-based gene expression analysis; microarray bioinformatics</t>
+  </si>
+  <si>
+    <t>snp analysis</t>
+  </si>
+  <si>
+    <t>snp analysis; snp genotyping; single nucleotide polymorphism analysis; variant calling; snp variant analysis; high-density snp genotyping; genome-wide snp profiling; allele frequency analysis</t>
+  </si>
+  <si>
+    <t>gene expression profiling</t>
+  </si>
+  <si>
+    <t>gene expression profiling; transcriptome profiling; gene expression analysis; mRNA profiling; expression microarray profiling; whole-transcriptome profiling; expression array analysis; RNA expression profiling</t>
+  </si>
+  <si>
+    <t>exon array</t>
+  </si>
+  <si>
+    <t>exon array; exon-level microarray; exon chip; exon expression array; exon junction array; exon-targeted microarray; Affymetrix exon array; exon microarray platform</t>
+  </si>
+  <si>
+    <t>sirna array</t>
+  </si>
+  <si>
+    <t>sirna array; siRNA microarray; sirna screening array; sirna expression array; siRNA library array; sirna chip; sirna microarray screening; sirna probe array</t>
+  </si>
+  <si>
+    <t>genome-wide snp analysis</t>
+  </si>
+  <si>
+    <t>genome-wide snp analysis; whole-genome snp analysis; genome-wide snp genotyping; genome-wide polymorphism analysis; genome-wide allele profiling; high-throughput snp genotyping</t>
+  </si>
+  <si>
+    <t>mutation genotyping array</t>
+  </si>
+  <si>
+    <t>mutation genotyping array; mutation detection microarray; mutation screening array; mutation-focused genotyping array; targeted mutation microarray; mutation analysis array; mutation detection array</t>
+  </si>
+  <si>
+    <t>comparative genomic hybridization</t>
+  </si>
+  <si>
+    <t>comparative genomic hybridization; cgh; comparative genomic hybridisation; genomic hybridization assay; chromosome comparative genomic hybridization; CGH assay</t>
+  </si>
+  <si>
+    <t>array-based cgh</t>
+  </si>
+  <si>
+    <t>array-based cgh; acgh; array cgh; microarray-based cgh; array comparative genomic hybridization; array comparative genomic hybridisation; array cgh assay</t>
+  </si>
+  <si>
+    <t>chip-on-chip</t>
+  </si>
+  <si>
+    <t>chip-on-chip; chip on chip; ChIP-chip; chip-on-chip assay; chromatin immunoprecipitation on chip; chromatin IP microarray; chip coupled immunoprecipitation; chromatin IP array</t>
+  </si>
+  <si>
+    <t>resequencing microarray</t>
+  </si>
+  <si>
+    <t>resequencing microarray; resequencing array; gene resequencing array; resequencing chip; resequencing microarray assay; resequencing microarray platform</t>
+  </si>
+  <si>
+    <t>transfection array screening</t>
+  </si>
+  <si>
+    <t>transfection array screening; transfection microarray screening; reverse-transfection array; arrayed transfection screening; cell microarray screening; transfection microarray assay</t>
+  </si>
+  <si>
+    <t>in-situ protein array synthesis</t>
+  </si>
+  <si>
+    <t>in-situ protein array synthesis; in situ protein microarray synthesis; on-chip protein synthesis; cell-free protein array synthesis; in-situ protein microarray fabrication; proteome microarray synthesis</t>
+  </si>
+  <si>
+    <t>high-frequency ultrasound</t>
+  </si>
+  <si>
+    <t>high-frequency ultrasound; high frequency ultrasound; hfus; high-frequency us; high-frequency sonography; high-frequency ultrasonography; high-frequency ultrasound imaging; megahertz ultrasound; ultrasound &gt;20 mhz</t>
+  </si>
+  <si>
+    <t>high-resolution micro-ct</t>
+  </si>
+  <si>
+    <t>high-resolution micro-ct; high resolution micro-ct; micro-computed tomography; micro ct; μct; micro-ct imaging; micro-computed tomography imaging; high-res μct; ex vivo micro-ct</t>
+  </si>
+  <si>
+    <t>high-resolution preclinical mri</t>
+  </si>
+  <si>
+    <t>high-resolution preclinical mri; high resolution preclinical mri; preclinical high-resolution mri; preclinical high-res mri; small-animal high-resolution mri; micro-mri; preclinical micro-mri; ultra-high-resolution preclinical mri</t>
+  </si>
+  <si>
+    <t>high-throughput dna sequencing</t>
+  </si>
+  <si>
+    <t>high-throughput dna sequencing; high throughput dna sequencing; high-throughput sequencing; next-generation sequencing; ngs; massively parallel sequencing; dna-seq; ht-dna-seq; illumina sequencing</t>
+  </si>
+  <si>
+    <t>high-throughput image-based drug screening</t>
+  </si>
+  <si>
+    <t>high-throughput image-based drug screening; high throughput image-based drug screening; high-content screening; hcs; high-content image-based screening; high-throughput microscopy screening; image-based hts; phenotypic screening</t>
+  </si>
+  <si>
+    <t>hindlimb paralysis</t>
+  </si>
+  <si>
+    <t>hindlimb paralysis; hind limb paralysis; hind-leg paralysis; paralysis of hindlimbs; posterior limb paralysis; hindleg paralysis; complete hindlimb paralysis; hindlimb plegia; inability to use hind legs; hindlimb motor deficit</t>
+  </si>
+  <si>
+    <t>imolecule</t>
+  </si>
+  <si>
+    <t>imolecule; i-molecule; i molecule; imolecule viewer; imolecule software; imolecule interactive; imolecule web viewer; imolecule database</t>
+  </si>
+  <si>
+    <t>in situ hybridization-based st</t>
+  </si>
+  <si>
+    <t>in situ hybridization-based st; in situ hybridization spatial transcriptomics; ish-based st; ish spatial transcriptomics; spatial transcriptomics (ish-based); in situ hybridization st; spatial ish; in situ ish st</t>
+  </si>
+  <si>
+    <t>in situ sequencing</t>
+  </si>
+  <si>
+    <t>in situ sequencing; in-situ sequencing; iss; in situ seq; in situ transcriptome sequencing; spatial in situ sequencing; molecular cartography; in situ RNA sequencing; in situ cDNA sequencing</t>
+  </si>
+  <si>
+    <t>intravital microscopy</t>
+  </si>
+  <si>
+    <t>intravital microscopy; intravital imaging; ivm; in vivo microscopy; live-animal microscopy; intravital multiphoton microscopy; intravital two-photon microscopy; intravital fluorescence microscopy; intravital confocal microscopy; intravital laser scanning microscopy</t>
+  </si>
+  <si>
+    <t>warm-spot test</t>
+  </si>
+  <si>
+    <t>warm-spot test; warm spot test; thermal preference test; temperature preference assay; warm-zone preference test; warm-plate preference test; thermal gradient assay; temperature choice test; heat-preference assay</t>
+  </si>
+  <si>
+    <t>whole-genome bisulfite sequencing</t>
+  </si>
+  <si>
+    <t>whole-genome bisulfite sequencing; whole genome bisulfite sequencing; wgbs; wgb-seq; genome-wide bisulfite sequencing; whole-genome bisulphite sequencing; bisulfite sequencing (whole genome); wg-bisulfite seq</t>
+  </si>
+  <si>
+    <t>whole-genome sequencing</t>
+  </si>
+  <si>
+    <t>wireframe representation</t>
+  </si>
+  <si>
+    <t>wireframe representation; wireframe model; wireframe rendering; wireframe view; skeletal model; skeletal representation; mesh wireframe; line-drawing model; edge-only rendering; structural wireframe</t>
+  </si>
+  <si>
+    <t>whole-genome sequencing; whole genome sequencing; wg-seq; genome sequencing; next-generation whole-genome sequencing; nnext-gen wgs; complete genome sequencing; full-genome sequencing</t>
   </si>
 </sst>
 </file>
@@ -3634,7 +3796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F7C088-4AE2-FE43-98E3-B1584DF0C0CC}">
-  <dimension ref="A1:B544"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.83203125" customWidth="1"/>
@@ -7993,6 +8155,222 @@
         <v>1067</v>
       </c>
     </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A545" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A546" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A547" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A548" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A549" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A550" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A551" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A552" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A553" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A554" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A555" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A556" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A557" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A558" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A559" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A560" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A561" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A562" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A563" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A564" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A565" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A566" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A567" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A568" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A569" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A570" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A571" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
